--- a/Bes(t)Poke SE216_SoftwareProcessModel.xlsx
+++ b/Bes(t)Poke SE216_SoftwareProcessModel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFA06E2-76E1-4F07-A1E6-CF54B7C201C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737EF5D3-8258-46C4-8FAF-7E07010B9ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{DD0626E2-1333-F643-A88B-8507C5CC965E}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="87">
   <si>
     <t>BACKLOG</t>
   </si>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t>Low</t>
-  </si>
-  <si>
-    <t>Developer</t>
   </si>
   <si>
     <t>On Hold</t>
@@ -155,9 +152,6 @@
     <t>Ensure mobile-friendly layout, improved UX.</t>
   </si>
   <si>
-    <t>Developer, Product Owner</t>
-  </si>
-  <si>
     <t>Database Planning</t>
   </si>
   <si>
@@ -176,9 +170,6 @@
     <t>Track commisions, display commision history, and manage commision statuses.</t>
   </si>
   <si>
-    <t>Enable users to apply adversarial noise processing (AI Shield) to portfolio items.</t>
-  </si>
-  <si>
     <t>Allow users to create public profiles featuring portfolios, pricing, and mandatory expertise tags.</t>
   </si>
   <si>
@@ -188,13 +179,7 @@
     <t>Creator Search &amp; Filter</t>
   </si>
   <si>
-    <t>Commision status tracking system</t>
-  </si>
-  <si>
     <t>Secure payment processing(İyizico).</t>
-  </si>
-  <si>
-    <t>AI Shield (e.g.,Glaze,Nightshade)</t>
   </si>
   <si>
     <t>Track commision status/history, revision count</t>
@@ -276,9 +261,6 @@
     <t>Allows for clear comminication between the client and the creator.</t>
   </si>
   <si>
-    <t>Two-way Review &amp; Rating System</t>
-  </si>
-  <si>
     <t>Creating Admin Panel</t>
   </si>
   <si>
@@ -288,12 +270,6 @@
     <t>Custom Order Form Creation</t>
   </si>
   <si>
-    <t>Adversarial Noise Processing Integration</t>
-  </si>
-  <si>
-    <t>Commision Placement Functionality</t>
-  </si>
-  <si>
     <t>Escrow Based Payment Gateway Integration</t>
   </si>
   <si>
@@ -301,9 +277,6 @@
   </si>
   <si>
     <t>Create a report system.</t>
-  </si>
-  <si>
-    <t>Two-way Report System</t>
   </si>
   <si>
     <t>Let users create creator-defined order forms.</t>
@@ -328,9 +301,6 @@
     <t>Enable users to demand revisions.</t>
   </si>
   <si>
-    <t>Revision Demand Functionality</t>
-  </si>
-  <si>
     <t>Allow users to fill the order forms(custom or default) and place their order.</t>
   </si>
   <si>
@@ -349,22 +319,49 @@
     <t>Manage accounts, disputes, and reports.</t>
   </si>
   <si>
-    <t>Verified Credentials System</t>
-  </si>
-  <si>
     <t>Notification System</t>
   </si>
   <si>
     <t>Triggering alerts for new messages, order status updates, and payment confirmations. (Email/In-App)</t>
   </si>
   <si>
-    <t>Implementation of diploma upload API</t>
-  </si>
-  <si>
     <t>Implement a notification system.</t>
   </si>
   <si>
-    <t>Implement a credentials verifying system.</t>
+    <t>Two-way Review,Rating &amp; Report System</t>
+  </si>
+  <si>
+    <t>Order Placement</t>
+  </si>
+  <si>
+    <t>Order Revision</t>
+  </si>
+  <si>
+    <t>Complete System Testing</t>
+  </si>
+  <si>
+    <t>Test the final product.</t>
+  </si>
+  <si>
+    <t>Order status tracking system</t>
+  </si>
+  <si>
+    <t>Complete system testing.</t>
+  </si>
+  <si>
+    <t>All Developers</t>
+  </si>
+  <si>
+    <t>All developers, Product Owner(Berk Mertoğlu)</t>
+  </si>
+  <si>
+    <t>All developers</t>
+  </si>
+  <si>
+    <t>Eralp,Berkay,Ata</t>
+  </si>
+  <si>
+    <t>Naz,Aslı,Zeynep</t>
   </si>
 </sst>
 </file>
@@ -502,11 +499,11 @@
       <charset val="162"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Century Gothic"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="162"/>
     </font>
   </fonts>
   <fills count="12">
@@ -897,7 +894,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -945,7 +942,6 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1060,9 +1056,6 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1075,7 +1068,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1147,11 +1140,14 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="101">
+  <dxfs count="91">
     <dxf>
       <fill>
         <patternFill>
@@ -1470,27 +1466,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF94EFFB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -1701,70 +1676,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
+          <bgColor rgb="FF94EFFB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2324,13 +2250,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1924050</xdr:colOff>
+      <xdr:colOff>1924049</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+      <xdr:rowOff>89065</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2330586</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>89064</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>58946</xdr:rowOff>
     </xdr:to>
@@ -2347,8 +2273,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8375650" y="7912100"/>
-          <a:ext cx="406536" cy="414546"/>
+          <a:off x="8376309" y="7699169"/>
+          <a:ext cx="658833" cy="524063"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2616,11 +2542,14 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="900" b="1">
+            <a:rPr lang="tr-TR" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>Atakan</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" sz="900" b="1">
+            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2629,15 +2558,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2273300</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>22225</xdr:rowOff>
+      <xdr:colOff>2243611</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>220147</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>247786</xdr:colOff>
+      <xdr:colOff>257299</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>157371</xdr:rowOff>
+      <xdr:rowOff>78203</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2652,8 +2581,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11214100" y="9128125"/>
-          <a:ext cx="463686" cy="414546"/>
+          <a:off x="11189689" y="8938615"/>
+          <a:ext cx="507506" cy="412237"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2921,11 +2850,570 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="900" b="1">
+            <a:rPr lang="tr-TR" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>Aslı</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" sz="900" b="1">
+            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>900546</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>376052</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>746249</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>193180</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Snip Single Corner Rectangle 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6173DAC9-4E42-4C26-893E-77C9ACADDDDA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12340442" y="7135091"/>
+          <a:ext cx="2012950" cy="1222375"/>
+        </a:xfrm>
+        <a:prstGeom prst="snip1Rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="114300" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>As a user, I want the</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="800" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> application </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>to be responsive and easy to use on multiple forms of devices like desktop, tablet, and phones, so that I can access it without</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="800" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> problem</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> from any device.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1"/>
+          <a:endParaRPr lang="en-US" sz="800" kern="1200" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>STATUS: Not Started</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="800">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>168234</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>98961</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>781792</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>118753</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Freeform 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CED351E7-526D-416A-B691-55D139E7AD9C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13775377" y="7986156"/>
+          <a:ext cx="613558" cy="573974"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="connsiteX0" fmla="*/ 298522 w 597046"/>
+            <a:gd name="connsiteY0" fmla="*/ 0 h 630113"/>
+            <a:gd name="connsiteX1" fmla="*/ 469972 w 597046"/>
+            <a:gd name="connsiteY1" fmla="*/ 165945 h 630113"/>
+            <a:gd name="connsiteX2" fmla="*/ 419755 w 597046"/>
+            <a:gd name="connsiteY2" fmla="*/ 283286 h 630113"/>
+            <a:gd name="connsiteX3" fmla="*/ 408034 w 597046"/>
+            <a:gd name="connsiteY3" fmla="*/ 290935 h 630113"/>
+            <a:gd name="connsiteX4" fmla="*/ 435155 w 597046"/>
+            <a:gd name="connsiteY4" fmla="*/ 302783 h 630113"/>
+            <a:gd name="connsiteX5" fmla="*/ 597046 w 597046"/>
+            <a:gd name="connsiteY5" fmla="*/ 583914 h 630113"/>
+            <a:gd name="connsiteX6" fmla="*/ 0 w 597046"/>
+            <a:gd name="connsiteY6" fmla="*/ 578243 h 630113"/>
+            <a:gd name="connsiteX7" fmla="*/ 159438 w 597046"/>
+            <a:gd name="connsiteY7" fmla="*/ 309073 h 630113"/>
+            <a:gd name="connsiteX8" fmla="*/ 194733 w 597046"/>
+            <a:gd name="connsiteY8" fmla="*/ 294670 h 630113"/>
+            <a:gd name="connsiteX9" fmla="*/ 177289 w 597046"/>
+            <a:gd name="connsiteY9" fmla="*/ 283286 h 630113"/>
+            <a:gd name="connsiteX10" fmla="*/ 127072 w 597046"/>
+            <a:gd name="connsiteY10" fmla="*/ 165945 h 630113"/>
+            <a:gd name="connsiteX11" fmla="*/ 298522 w 597046"/>
+            <a:gd name="connsiteY11" fmla="*/ 0 h 630113"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX0" y="connsiteY0"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX1" y="connsiteY1"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX2" y="connsiteY2"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX3" y="connsiteY3"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX4" y="connsiteY4"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX5" y="connsiteY5"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX6" y="connsiteY6"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX7" y="connsiteY7"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX8" y="connsiteY8"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX9" y="connsiteY9"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX10" y="connsiteY10"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="connsiteX11" y="connsiteY11"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="597046" h="630113">
+              <a:moveTo>
+                <a:pt x="298522" y="0"/>
+              </a:moveTo>
+              <a:cubicBezTo>
+                <a:pt x="393211" y="0"/>
+                <a:pt x="469972" y="74296"/>
+                <a:pt x="469972" y="165945"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="469972" y="211769"/>
+                <a:pt x="450782" y="253256"/>
+                <a:pt x="419755" y="283286"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="408034" y="290935"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="435155" y="302783"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="525950" y="364596"/>
+                <a:pt x="526507" y="507747"/>
+                <a:pt x="597046" y="583914"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="398031" y="650070"/>
+                <a:pt x="146632" y="642511"/>
+                <a:pt x="0" y="578243"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="77087" y="502076"/>
+                <a:pt x="58410" y="371684"/>
+                <a:pt x="159438" y="309073"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="194733" y="294670"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="177289" y="283286"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="146262" y="253256"/>
+                <a:pt x="127072" y="211769"/>
+                <a:pt x="127072" y="165945"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="127072" y="74296"/>
+                <a:pt x="203833" y="0"/>
+                <a:pt x="298522" y="0"/>
+              </a:cubicBezTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+        <a:sp3d contourW="12700">
+          <a:bevelT w="38100" h="25400" prst="coolSlant"/>
+          <a:contourClr>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="65000"/>
+            </a:schemeClr>
+          </a:contourClr>
+        </a:sp3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="900" b="1">
+              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Zeynep</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="900" b="1">
+            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3705,11 +4193,14 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="900" b="1">
+            <a:rPr lang="tr-TR" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>Ata</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" sz="900" b="1">
+            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4018,13 +4509,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>860426</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>4445</xdr:rowOff>
+      <xdr:colOff>860425</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>193344</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1266962</xdr:colOff>
+      <xdr:colOff>1410268</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>131336</xdr:rowOff>
     </xdr:to>
@@ -4041,8 +4532,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9257666" y="8896985"/>
-          <a:ext cx="406536" cy="401211"/>
+          <a:off x="9253798" y="8780060"/>
+          <a:ext cx="549843" cy="483903"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -4310,11 +4801,14 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="900" b="1">
+            <a:rPr lang="tr-TR" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>Naz</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" sz="900" b="1">
+            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4323,15 +4817,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>368300</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:colOff>277314</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>223824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>774836</xdr:colOff>
+      <xdr:colOff>887103</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>158006</xdr:rowOff>
+      <xdr:rowOff>181970</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4346,8 +4840,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11257280" y="7551420"/>
-          <a:ext cx="406536" cy="401846"/>
+          <a:off x="11161404" y="7445764"/>
+          <a:ext cx="609789" cy="504057"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -4615,11 +5109,14 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="900" b="1">
+            <a:rPr lang="tr-TR" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>Berkay</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" sz="900" b="1">
+            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4874,15 +5371,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>91440</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:colOff>45946</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>261583</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>497976</xdr:colOff>
+      <xdr:colOff>636895</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>167531</xdr:rowOff>
+      <xdr:rowOff>190277</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4897,8 +5394,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13144500" y="8923020"/>
-          <a:ext cx="406536" cy="411371"/>
+          <a:off x="13090931" y="8848299"/>
+          <a:ext cx="590949" cy="474605"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5169,7 +5666,7 @@
             <a:rPr lang="tr-TR" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>Atakan</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="900" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
@@ -5470,15 +5967,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1752600</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:colOff>1763973</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>238837</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2159136</xdr:colOff>
+      <xdr:colOff>2274627</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>144671</xdr:rowOff>
+      <xdr:rowOff>178791</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5493,8 +5990,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14805660" y="7528560"/>
-          <a:ext cx="406536" cy="411371"/>
+          <a:off x="14808958" y="7460777"/>
+          <a:ext cx="510654" cy="485865"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5778,7 +6275,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>Eralp</a:t>
           </a:r>
           <a:endParaRPr kumimoji="0" lang="en-US" sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
             <a:ln>
@@ -6214,7 +6711,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>As a user with client role, I want to view my commision history and the current status of the commisions I ordered, so that I can track my purchases and know when ı will recieve the product.</a:t>
+            <a:t>As a user, I want to view my order history and my current orders, so that I can track my purchases and know when ı will recieve the product.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -6260,15 +6757,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1554616</xdr:colOff>
+      <xdr:colOff>1571740</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>182502</xdr:rowOff>
+      <xdr:rowOff>128427</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1961152</xdr:colOff>
+      <xdr:colOff>2029148</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>43328</xdr:rowOff>
+      <xdr:rowOff>51371</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6283,8 +6780,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7464169" y="7453928"/>
-          <a:ext cx="406536" cy="412060"/>
+          <a:off x="7479380" y="7371708"/>
+          <a:ext cx="457408" cy="470899"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -6552,11 +7049,14 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="900" b="1">
+            <a:rPr lang="tr-TR" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>Berk</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" sz="900" b="1">
+            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -6857,11 +7357,14 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="900" b="1">
+            <a:rPr lang="tr-TR" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>Aslı</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" sz="900" b="1">
+            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -6869,23 +7372,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1099063</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1209</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>145914</xdr:rowOff>
+      <xdr:rowOff>212175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>610653</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>56906</xdr:rowOff>
+      <xdr:colOff>2313259</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>202649</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Snip Single Corner Rectangle 20">
+        <xdr:cNvPr id="8" name="Snip Single Corner Rectangle 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47A1892A-3785-4AB6-AB3D-45CFBF46664F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71BF68D1-63EC-4CFC-AA4B-3D2E199FA9CC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6893,14 +7396,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7008616" y="7968574"/>
-          <a:ext cx="2000250" cy="1289077"/>
+          <a:off x="8394932" y="7902513"/>
+          <a:ext cx="2312050" cy="1068998"/>
         </a:xfrm>
         <a:prstGeom prst="snip1Rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent2">
+          <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
             <a:lumOff val="80000"/>
           </a:schemeClr>
@@ -7031,67 +7534,27 @@
         </a:lstStyle>
         <a:p>
           <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0">
+            <a:rPr lang="tr-TR" sz="800" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
+              <a:effectLst/>
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>As a user</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> with creator role, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>I want apply AI shield to my portfolio item without using</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> another program</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>,so that I</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> can upload my portfolio without fearing it will be stolen for unauthorised usage in AI generation.</a:t>
+            <a:t>As a user with creator role, I want to view my commision history and the current status of the commisions I recieved, so that I can track work history and know what projects are needed to be done.</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="800">
+          <a:endParaRPr lang="tr-TR" sz="800" kern="1200" baseline="0">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -7105,26 +7568,18 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>STATUS: Not</a:t>
+            <a:t>STATUS: Not Started</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> Started</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="800">
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="800" kern="1200" baseline="0">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -7134,22 +7589,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>138458</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>42640</xdr:rowOff>
+      <xdr:colOff>1541222</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>229773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>544994</xdr:colOff>
+      <xdr:colOff>2040739</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>180988</xdr:rowOff>
+      <xdr:rowOff>97193</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Freeform 11">
+        <xdr:cNvPr id="11" name="Freeform 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC9EE5F5-25F1-46B7-92D3-B7D56821C467}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B74BED14-D51A-4FC2-9BE6-4172A5E07629}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7157,8 +7612,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8536671" y="8967768"/>
-          <a:ext cx="406536" cy="413965"/>
+          <a:off x="9934945" y="8729004"/>
+          <a:ext cx="499517" cy="406681"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -7429,7 +7884,7 @@
             <a:rPr lang="tr-TR" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>Ata</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="900" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
@@ -7441,540 +7896,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1736225</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>71498</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>355506</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>61973</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="Snip Single Corner Rectangle 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71BF68D1-63EC-4CFC-AA4B-3D2E199FA9CC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10134438" y="8169775"/>
-          <a:ext cx="2307685" cy="1092943"/>
-        </a:xfrm>
-        <a:prstGeom prst="snip1Rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="114300" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-            <a:prstClr val="black">
-              <a:alpha val="40000"/>
-            </a:prstClr>
-          </a:outerShdw>
-        </a:effectLst>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="en-US"/>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>As a user with creator role, I want to view my commision history and the current status of the commisions I recieved, so that I can track work history and know what projects are needed to be done.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="tr-TR" sz="800" kern="1200" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>STATUS: Not Started</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="800" kern="1200" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1037131</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>340894</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>167531</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="Freeform 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B74BED14-D51A-4FC2-9BE6-4172A5E07629}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11925710" y="8823559"/>
-          <a:ext cx="496895" cy="407761"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 298522 w 597046"/>
-            <a:gd name="connsiteY0" fmla="*/ 0 h 630113"/>
-            <a:gd name="connsiteX1" fmla="*/ 469972 w 597046"/>
-            <a:gd name="connsiteY1" fmla="*/ 165945 h 630113"/>
-            <a:gd name="connsiteX2" fmla="*/ 419755 w 597046"/>
-            <a:gd name="connsiteY2" fmla="*/ 283286 h 630113"/>
-            <a:gd name="connsiteX3" fmla="*/ 408034 w 597046"/>
-            <a:gd name="connsiteY3" fmla="*/ 290935 h 630113"/>
-            <a:gd name="connsiteX4" fmla="*/ 435155 w 597046"/>
-            <a:gd name="connsiteY4" fmla="*/ 302783 h 630113"/>
-            <a:gd name="connsiteX5" fmla="*/ 597046 w 597046"/>
-            <a:gd name="connsiteY5" fmla="*/ 583914 h 630113"/>
-            <a:gd name="connsiteX6" fmla="*/ 0 w 597046"/>
-            <a:gd name="connsiteY6" fmla="*/ 578243 h 630113"/>
-            <a:gd name="connsiteX7" fmla="*/ 159438 w 597046"/>
-            <a:gd name="connsiteY7" fmla="*/ 309073 h 630113"/>
-            <a:gd name="connsiteX8" fmla="*/ 194733 w 597046"/>
-            <a:gd name="connsiteY8" fmla="*/ 294670 h 630113"/>
-            <a:gd name="connsiteX9" fmla="*/ 177289 w 597046"/>
-            <a:gd name="connsiteY9" fmla="*/ 283286 h 630113"/>
-            <a:gd name="connsiteX10" fmla="*/ 127072 w 597046"/>
-            <a:gd name="connsiteY10" fmla="*/ 165945 h 630113"/>
-            <a:gd name="connsiteX11" fmla="*/ 298522 w 597046"/>
-            <a:gd name="connsiteY11" fmla="*/ 0 h 630113"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX3" y="connsiteY3"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX4" y="connsiteY4"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX5" y="connsiteY5"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX6" y="connsiteY6"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX7" y="connsiteY7"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX8" y="connsiteY8"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX9" y="connsiteY9"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX10" y="connsiteY10"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX11" y="connsiteY11"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="597046" h="630113">
-              <a:moveTo>
-                <a:pt x="298522" y="0"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="393211" y="0"/>
-                <a:pt x="469972" y="74296"/>
-                <a:pt x="469972" y="165945"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="469972" y="211769"/>
-                <a:pt x="450782" y="253256"/>
-                <a:pt x="419755" y="283286"/>
-              </a:cubicBezTo>
-              <a:lnTo>
-                <a:pt x="408034" y="290935"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="435155" y="302783"/>
-              </a:lnTo>
-              <a:cubicBezTo>
-                <a:pt x="525950" y="364596"/>
-                <a:pt x="526507" y="507747"/>
-                <a:pt x="597046" y="583914"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="398031" y="650070"/>
-                <a:pt x="146632" y="642511"/>
-                <a:pt x="0" y="578243"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="77087" y="502076"/>
-                <a:pt x="58410" y="371684"/>
-                <a:pt x="159438" y="309073"/>
-              </a:cubicBezTo>
-              <a:lnTo>
-                <a:pt x="194733" y="294670"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="177289" y="283286"/>
-              </a:lnTo>
-              <a:cubicBezTo>
-                <a:pt x="146262" y="253256"/>
-                <a:pt x="127072" y="211769"/>
-                <a:pt x="127072" y="165945"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="127072" y="74296"/>
-                <a:pt x="203833" y="0"/>
-                <a:pt x="298522" y="0"/>
-              </a:cubicBezTo>
-              <a:close/>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="7030A0"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-            <a:prstClr val="black">
-              <a:alpha val="40000"/>
-            </a:prstClr>
-          </a:outerShdw>
-        </a:effectLst>
-        <a:scene3d>
-          <a:camera prst="orthographicFront"/>
-          <a:lightRig rig="threePt" dir="t"/>
-        </a:scene3d>
-        <a:sp3d contourW="12700">
-          <a:bevelT w="38100" h="25400" prst="coolSlant"/>
-          <a:contourClr>
-            <a:schemeClr val="bg1">
-              <a:lumMod val="65000"/>
-            </a:schemeClr>
-          </a:contourClr>
-        </a:sp3d>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="en-US"/>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="900" b="1">
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Dev</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="900" b="1">
-            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>408562</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>298639</xdr:rowOff>
+      <xdr:colOff>1100223</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>228300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1577502</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>108139</xdr:rowOff>
+      <xdr:colOff>1073409</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>72969</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7989,8 +7920,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12495179" y="6718894"/>
-          <a:ext cx="2133600" cy="1211905"/>
+          <a:off x="11990961" y="7379377"/>
+          <a:ext cx="2141956" cy="1192823"/>
         </a:xfrm>
         <a:prstGeom prst="snip1Rect">
           <a:avLst/>
@@ -8221,15 +8152,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>880678</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>86652</xdr:rowOff>
+      <xdr:colOff>453775</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>51371</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1287214</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>223703</xdr:rowOff>
+      <xdr:colOff>1053101</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>235426</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8244,8 +8175,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13934941" y="7526178"/>
-          <a:ext cx="406536" cy="407762"/>
+          <a:off x="13510517" y="8390562"/>
+          <a:ext cx="599326" cy="458033"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -8516,581 +8447,7 @@
             <a:rPr lang="tr-TR" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Dev</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="900" b="1">
-            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1520621</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>187796</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3528763</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>188360</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="Snip Single Corner Rectangle 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CE48FEB-302F-494F-B641-82F375504231}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14577363" y="7979032"/>
-          <a:ext cx="2008142" cy="1096474"/>
-        </a:xfrm>
-        <a:prstGeom prst="snip1Rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="114300" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-            <a:prstClr val="black">
-              <a:alpha val="40000"/>
-            </a:prstClr>
-          </a:outerShdw>
-        </a:effectLst>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="en-US"/>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>As a user</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>I want portfolio</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> items like certificates and diplomas to be verified, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>so that I</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> can be able to trust the abilities of the creators.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="800">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>STATUS: Not</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> Started</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="800">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2807369</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>225760</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3213905</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>92444</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Freeform 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C44714B-4B91-4CED-A29E-BE77A508A9DE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15864111" y="8838929"/>
-          <a:ext cx="406536" cy="414639"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 298522 w 597046"/>
-            <a:gd name="connsiteY0" fmla="*/ 0 h 630113"/>
-            <a:gd name="connsiteX1" fmla="*/ 469972 w 597046"/>
-            <a:gd name="connsiteY1" fmla="*/ 165945 h 630113"/>
-            <a:gd name="connsiteX2" fmla="*/ 419755 w 597046"/>
-            <a:gd name="connsiteY2" fmla="*/ 283286 h 630113"/>
-            <a:gd name="connsiteX3" fmla="*/ 408034 w 597046"/>
-            <a:gd name="connsiteY3" fmla="*/ 290935 h 630113"/>
-            <a:gd name="connsiteX4" fmla="*/ 435155 w 597046"/>
-            <a:gd name="connsiteY4" fmla="*/ 302783 h 630113"/>
-            <a:gd name="connsiteX5" fmla="*/ 597046 w 597046"/>
-            <a:gd name="connsiteY5" fmla="*/ 583914 h 630113"/>
-            <a:gd name="connsiteX6" fmla="*/ 0 w 597046"/>
-            <a:gd name="connsiteY6" fmla="*/ 578243 h 630113"/>
-            <a:gd name="connsiteX7" fmla="*/ 159438 w 597046"/>
-            <a:gd name="connsiteY7" fmla="*/ 309073 h 630113"/>
-            <a:gd name="connsiteX8" fmla="*/ 194733 w 597046"/>
-            <a:gd name="connsiteY8" fmla="*/ 294670 h 630113"/>
-            <a:gd name="connsiteX9" fmla="*/ 177289 w 597046"/>
-            <a:gd name="connsiteY9" fmla="*/ 283286 h 630113"/>
-            <a:gd name="connsiteX10" fmla="*/ 127072 w 597046"/>
-            <a:gd name="connsiteY10" fmla="*/ 165945 h 630113"/>
-            <a:gd name="connsiteX11" fmla="*/ 298522 w 597046"/>
-            <a:gd name="connsiteY11" fmla="*/ 0 h 630113"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX3" y="connsiteY3"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX4" y="connsiteY4"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX5" y="connsiteY5"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX6" y="connsiteY6"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX7" y="connsiteY7"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX8" y="connsiteY8"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX9" y="connsiteY9"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX10" y="connsiteY10"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX11" y="connsiteY11"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="597046" h="630113">
-              <a:moveTo>
-                <a:pt x="298522" y="0"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="393211" y="0"/>
-                <a:pt x="469972" y="74296"/>
-                <a:pt x="469972" y="165945"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="469972" y="211769"/>
-                <a:pt x="450782" y="253256"/>
-                <a:pt x="419755" y="283286"/>
-              </a:cubicBezTo>
-              <a:lnTo>
-                <a:pt x="408034" y="290935"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="435155" y="302783"/>
-              </a:lnTo>
-              <a:cubicBezTo>
-                <a:pt x="525950" y="364596"/>
-                <a:pt x="526507" y="507747"/>
-                <a:pt x="597046" y="583914"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="398031" y="650070"/>
-                <a:pt x="146632" y="642511"/>
-                <a:pt x="0" y="578243"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="77087" y="502076"/>
-                <a:pt x="58410" y="371684"/>
-                <a:pt x="159438" y="309073"/>
-              </a:cubicBezTo>
-              <a:lnTo>
-                <a:pt x="194733" y="294670"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="177289" y="283286"/>
-              </a:lnTo>
-              <a:cubicBezTo>
-                <a:pt x="146262" y="253256"/>
-                <a:pt x="127072" y="211769"/>
-                <a:pt x="127072" y="165945"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="127072" y="74296"/>
-                <a:pt x="203833" y="0"/>
-                <a:pt x="298522" y="0"/>
-              </a:cubicBezTo>
-              <a:close/>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent4">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-            <a:prstClr val="black">
-              <a:alpha val="40000"/>
-            </a:prstClr>
-          </a:outerShdw>
-        </a:effectLst>
-        <a:scene3d>
-          <a:camera prst="orthographicFront"/>
-          <a:lightRig rig="threePt" dir="t"/>
-        </a:scene3d>
-        <a:sp3d contourW="12700">
-          <a:bevelT w="38100" h="25400" prst="coolSlant"/>
-          <a:contourClr>
-            <a:schemeClr val="bg1">
-              <a:lumMod val="65000"/>
-            </a:schemeClr>
-          </a:contourClr>
-        </a:sp3d>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="en-US"/>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="900" b="1">
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>Berkay</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="900" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
@@ -9904,257 +9261,12 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="900" b="1">
+            <a:rPr lang="tr-TR" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>Naz</a:t>
           </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1036320</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>365760</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>877570</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>187960</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="Snip Single Corner Rectangle 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A50B6769-CB60-F948-A831-AD3BBB377EF3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11925300" y="6766560"/>
-          <a:ext cx="2005330" cy="1216660"/>
-        </a:xfrm>
-        <a:prstGeom prst="snip1Rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="114300" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-            <a:prstClr val="black">
-              <a:alpha val="40000"/>
-            </a:prstClr>
-          </a:outerShdw>
-        </a:effectLst>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="en-US"/>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>As a user, I want the</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> application </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>to be responsive and easy to use on multiple forms of devices like desktop, tablet, and phones, so that I can access it without</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> problem</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> from any device.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1"/>
-          <a:endParaRPr lang="en-US" sz="800" kern="1200" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>STATUS: Not Started</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="800">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst/>
+          <a:endParaRPr lang="en-US" sz="900" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
           </a:endParaRPr>
         </a:p>
@@ -10462,7 +9574,7 @@
             <a:rPr lang="tr-TR" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>Eralp</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="900" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
@@ -10474,321 +9586,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>294640</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1147396</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>419100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>739140</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Freeform 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16513DDA-AEE6-5545-A27C-5391206B1CD5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13347700" y="7698740"/>
-          <a:ext cx="444500" cy="462280"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 298522 w 597046"/>
-            <a:gd name="connsiteY0" fmla="*/ 0 h 630113"/>
-            <a:gd name="connsiteX1" fmla="*/ 469972 w 597046"/>
-            <a:gd name="connsiteY1" fmla="*/ 165945 h 630113"/>
-            <a:gd name="connsiteX2" fmla="*/ 419755 w 597046"/>
-            <a:gd name="connsiteY2" fmla="*/ 283286 h 630113"/>
-            <a:gd name="connsiteX3" fmla="*/ 408034 w 597046"/>
-            <a:gd name="connsiteY3" fmla="*/ 290935 h 630113"/>
-            <a:gd name="connsiteX4" fmla="*/ 435155 w 597046"/>
-            <a:gd name="connsiteY4" fmla="*/ 302783 h 630113"/>
-            <a:gd name="connsiteX5" fmla="*/ 597046 w 597046"/>
-            <a:gd name="connsiteY5" fmla="*/ 583914 h 630113"/>
-            <a:gd name="connsiteX6" fmla="*/ 0 w 597046"/>
-            <a:gd name="connsiteY6" fmla="*/ 578243 h 630113"/>
-            <a:gd name="connsiteX7" fmla="*/ 159438 w 597046"/>
-            <a:gd name="connsiteY7" fmla="*/ 309073 h 630113"/>
-            <a:gd name="connsiteX8" fmla="*/ 194733 w 597046"/>
-            <a:gd name="connsiteY8" fmla="*/ 294670 h 630113"/>
-            <a:gd name="connsiteX9" fmla="*/ 177289 w 597046"/>
-            <a:gd name="connsiteY9" fmla="*/ 283286 h 630113"/>
-            <a:gd name="connsiteX10" fmla="*/ 127072 w 597046"/>
-            <a:gd name="connsiteY10" fmla="*/ 165945 h 630113"/>
-            <a:gd name="connsiteX11" fmla="*/ 298522 w 597046"/>
-            <a:gd name="connsiteY11" fmla="*/ 0 h 630113"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX3" y="connsiteY3"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX4" y="connsiteY4"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX5" y="connsiteY5"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX6" y="connsiteY6"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX7" y="connsiteY7"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX8" y="connsiteY8"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX9" y="connsiteY9"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX10" y="connsiteY10"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX11" y="connsiteY11"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="597046" h="630113">
-              <a:moveTo>
-                <a:pt x="298522" y="0"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="393211" y="0"/>
-                <a:pt x="469972" y="74296"/>
-                <a:pt x="469972" y="165945"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="469972" y="211769"/>
-                <a:pt x="450782" y="253256"/>
-                <a:pt x="419755" y="283286"/>
-              </a:cubicBezTo>
-              <a:lnTo>
-                <a:pt x="408034" y="290935"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="435155" y="302783"/>
-              </a:lnTo>
-              <a:cubicBezTo>
-                <a:pt x="525950" y="364596"/>
-                <a:pt x="526507" y="507747"/>
-                <a:pt x="597046" y="583914"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="398031" y="650070"/>
-                <a:pt x="146632" y="642511"/>
-                <a:pt x="0" y="578243"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="77087" y="502076"/>
-                <a:pt x="58410" y="371684"/>
-                <a:pt x="159438" y="309073"/>
-              </a:cubicBezTo>
-              <a:lnTo>
-                <a:pt x="194733" y="294670"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="177289" y="283286"/>
-              </a:lnTo>
-              <a:cubicBezTo>
-                <a:pt x="146262" y="253256"/>
-                <a:pt x="127072" y="211769"/>
-                <a:pt x="127072" y="165945"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="127072" y="74296"/>
-                <a:pt x="203833" y="0"/>
-                <a:pt x="298522" y="0"/>
-              </a:cubicBezTo>
-              <a:close/>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="C00000"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-            <a:prstClr val="black">
-              <a:alpha val="40000"/>
-            </a:prstClr>
-          </a:outerShdw>
-        </a:effectLst>
-        <a:scene3d>
-          <a:camera prst="orthographicFront"/>
-          <a:lightRig rig="threePt" dir="t"/>
-        </a:scene3d>
-        <a:sp3d contourW="12700">
-          <a:bevelT w="38100" h="25400" prst="coolSlant"/>
-          <a:contourClr>
-            <a:schemeClr val="bg1">
-              <a:lumMod val="65000"/>
-            </a:schemeClr>
-          </a:contourClr>
-        </a:sp3d>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="en-US"/>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="900" b="1">
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Dev</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1090246</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3488835</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>59055</xdr:rowOff>
+      <xdr:colOff>1374285</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10803,8 +9610,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14149754" y="7420708"/>
-          <a:ext cx="2398589" cy="1137578"/>
+          <a:off x="12043996" y="6858000"/>
+          <a:ext cx="2398589" cy="1163955"/>
         </a:xfrm>
         <a:prstGeom prst="snip1Rect">
           <a:avLst/>
@@ -10996,15 +9803,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2713011</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>56956</xdr:rowOff>
+      <xdr:colOff>522260</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>152206</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3119547</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>191849</xdr:rowOff>
+      <xdr:colOff>1104899</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11019,8 +9826,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15768161" y="8459186"/>
-          <a:ext cx="406536" cy="411371"/>
+          <a:off x="13590560" y="7715056"/>
+          <a:ext cx="582639" cy="476444"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -11291,7 +10098,7 @@
             <a:rPr lang="tr-TR" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>Berk</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -18654,6 +17461,222 @@
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1104900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2533030</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>32678</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Snip Single Corner Rectangle 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5215A528-8779-47E1-82F2-A84A40DB6352}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2415540" y="8404860"/>
+          <a:ext cx="2312050" cy="1068998"/>
+        </a:xfrm>
+        <a:prstGeom prst="snip1Rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="114300" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1800" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="800" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>As a user with creator role, I want to view my commision history and the current status of the commisions I recieved, so that I can track work history and know what projects are needed to be done.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="tr-TR" sz="800" kern="1200" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>STATUS: Not Started</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="800" kern="1200" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -18987,176 +18010,172 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="91.95" customHeight="1">
-      <c r="A1" s="73" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="74"/>
+      <c r="A1" s="71" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="72"/>
     </row>
     <row r="2" spans="1:2" ht="45" customHeight="1">
-      <c r="A2" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33" t="s">
         <v>23</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" customHeight="1">
-      <c r="A3" s="34">
+      <c r="A3" s="33">
         <v>1</v>
       </c>
-      <c r="B3" s="41" t="s">
-        <v>36</v>
+      <c r="B3" s="40" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="45" customHeight="1">
-      <c r="A4" s="34">
+      <c r="A4" s="33">
         <v>2</v>
       </c>
-      <c r="B4" s="41" t="s">
-        <v>80</v>
+      <c r="B4" s="40" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" customHeight="1">
-      <c r="A5" s="34">
+      <c r="A5" s="33">
         <v>3</v>
       </c>
-      <c r="B5" s="41" t="s">
-        <v>43</v>
+      <c r="B5" s="40" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45" customHeight="1">
-      <c r="A6" s="34">
+      <c r="A6" s="33">
         <v>4</v>
       </c>
-      <c r="B6" s="41" t="s">
-        <v>79</v>
+      <c r="B6" s="40" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" customHeight="1">
-      <c r="A7" s="34">
+      <c r="A7" s="33">
         <v>5</v>
       </c>
-      <c r="B7" s="41" t="s">
-        <v>38</v>
+      <c r="B7" s="40" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" customHeight="1">
-      <c r="A8" s="34">
+      <c r="A8" s="33">
         <v>6</v>
       </c>
-      <c r="B8" s="41" t="s">
-        <v>68</v>
+      <c r="B8" s="40" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45" customHeight="1">
-      <c r="A9" s="34">
+      <c r="A9" s="33">
         <v>7</v>
       </c>
-      <c r="B9" s="41" t="s">
-        <v>69</v>
+      <c r="B9" s="40" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="45" customHeight="1">
-      <c r="A10" s="34">
+      <c r="A10" s="33">
         <v>8</v>
       </c>
-      <c r="B10" s="41" t="s">
-        <v>73</v>
+      <c r="B10" s="40" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="45" customHeight="1">
-      <c r="A11" s="34">
+      <c r="A11" s="33">
         <v>9</v>
       </c>
-      <c r="B11" s="41" t="s">
-        <v>74</v>
+      <c r="B11" s="40" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" customHeight="1">
-      <c r="A12" s="34">
+      <c r="A12" s="33">
         <v>10</v>
       </c>
-      <c r="B12" s="41" t="s">
-        <v>78</v>
+      <c r="B12" s="40" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" customHeight="1">
-      <c r="A13" s="34">
+      <c r="A13" s="33">
         <v>11</v>
       </c>
-      <c r="B13" s="41" t="s">
-        <v>42</v>
+      <c r="B13" s="40" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="45" customHeight="1">
-      <c r="A14" s="34">
+      <c r="A14" s="33">
         <v>12</v>
       </c>
-      <c r="B14" s="65" t="s">
-        <v>87</v>
+      <c r="B14" s="40" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="45" customHeight="1">
-      <c r="A15" s="34">
+      <c r="A15" s="33">
         <v>13</v>
       </c>
-      <c r="B15" s="41" t="s">
-        <v>39</v>
+      <c r="B15" s="40" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" customHeight="1">
-      <c r="A16" s="34">
+      <c r="A16" s="33">
         <v>14</v>
       </c>
-      <c r="B16" s="41" t="s">
-        <v>41</v>
+      <c r="B16" s="40" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="45" customHeight="1">
-      <c r="A17" s="34">
+      <c r="A17" s="33">
         <v>15</v>
       </c>
-      <c r="B17" s="41" t="s">
-        <v>65</v>
+      <c r="B17" s="64" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="45" customHeight="1">
-      <c r="A18" s="34">
+      <c r="A18" s="33">
         <v>16</v>
       </c>
-      <c r="B18" s="41" t="s">
-        <v>66</v>
+      <c r="B18" s="40" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="45" customHeight="1">
-      <c r="A19" s="34">
+      <c r="A19" s="33">
         <v>17</v>
       </c>
-      <c r="B19" s="65" t="s">
-        <v>40</v>
+      <c r="B19" s="40" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="45" customHeight="1">
-      <c r="A20" s="34">
+      <c r="A20" s="33">
         <v>18</v>
       </c>
-      <c r="B20" s="41" t="s">
-        <v>25</v>
+      <c r="B20" s="40" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45" customHeight="1">
-      <c r="A21" s="34">
+      <c r="A21" s="33">
         <v>19</v>
-      </c>
-      <c r="B21" s="41" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="45" customHeight="1">
-      <c r="A22" s="34">
+      <c r="A22" s="33">
         <v>20</v>
       </c>
-      <c r="B22" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -19188,143 +18207,160 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.6">
-      <c r="B1" s="90" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
+      <c r="B1" s="88" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
     </row>
     <row r="2" spans="1:15" ht="27.6">
-      <c r="B2" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="36" t="s">
+      <c r="B2" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="G2" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="H2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="35" t="s">
         <v>8</v>
       </c>
       <c r="M2" s="11"/>
     </row>
     <row r="3" spans="1:15" ht="46.05" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="57" t="s">
+      <c r="A3" s="62"/>
+      <c r="B3" s="56" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="60">
+        <v>47000</v>
+      </c>
+      <c r="G3" s="60">
+        <v>47002</v>
+      </c>
+      <c r="H3" s="63">
+        <v>3</v>
+      </c>
+      <c r="I3" s="56" t="s">
         <v>35</v>
-      </c>
-      <c r="C3" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="61">
-        <v>46999</v>
-      </c>
-      <c r="G3" s="61">
-        <v>47024</v>
-      </c>
-      <c r="H3" s="64">
-        <v>26</v>
-      </c>
-      <c r="I3" s="57" t="s">
-        <v>37</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="62" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="60" t="s">
+      <c r="A4" s="62"/>
+      <c r="B4" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="61">
-        <v>46999</v>
-      </c>
-      <c r="G4" s="61">
-        <v>47007</v>
-      </c>
-      <c r="H4" s="64">
-        <v>9</v>
-      </c>
-      <c r="I4" s="40" t="s">
-        <v>72</v>
+      <c r="F4" s="60">
+        <v>47003</v>
+      </c>
+      <c r="G4" s="60">
+        <v>47003</v>
+      </c>
+      <c r="H4" s="63">
+        <v>1</v>
+      </c>
+      <c r="I4" s="39" t="s">
+        <v>63</v>
       </c>
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A5" s="63"/>
-      <c r="B5" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="62" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="60" t="s">
+      <c r="A5" s="62"/>
+      <c r="B5" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="61">
-        <v>47007</v>
-      </c>
-      <c r="G5" s="61">
-        <v>47017</v>
-      </c>
-      <c r="H5" s="64">
-        <v>10</v>
-      </c>
-      <c r="I5" s="57" t="s">
-        <v>52</v>
+      <c r="F5" s="60">
+        <v>47004</v>
+      </c>
+      <c r="G5" s="60">
+        <v>47004</v>
+      </c>
+      <c r="H5" s="63">
+        <v>1</v>
+      </c>
+      <c r="I5" s="56" t="s">
+        <v>47</v>
       </c>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="22.05" customHeight="1">
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="3"/>
+      <c r="A6" s="58"/>
+      <c r="B6" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="60">
+        <v>47007</v>
+      </c>
+      <c r="G6" s="60">
+        <v>47008</v>
+      </c>
+      <c r="H6" s="63">
+        <v>2</v>
+      </c>
+      <c r="I6" s="56" t="s">
+        <v>33</v>
+      </c>
       <c r="M6" s="3"/>
     </row>
     <row r="7" spans="1:15" ht="22.05" customHeight="1">
@@ -19501,162 +18537,162 @@
       <c r="G22" s="9"/>
       <c r="H22" s="10">
         <f>MAX(G3:G21)-MIN(F3:F21)+1</f>
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="I22" s="8"/>
     </row>
     <row r="23" spans="2:14" ht="22.05" customHeight="1"/>
     <row r="24" spans="2:14" ht="45" customHeight="1">
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="76"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="84"/>
-      <c r="K24" s="84"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="84"/>
-      <c r="N24" s="85"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="82"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="83"/>
     </row>
     <row r="25" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B25" s="78"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
-      <c r="L25" s="86"/>
-      <c r="M25" s="86"/>
-      <c r="N25" s="87"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="78"/>
+      <c r="E25" s="84"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="85"/>
     </row>
     <row r="26" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B26" s="78"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
-      <c r="L26" s="86"/>
-      <c r="M26" s="86"/>
-      <c r="N26" s="87"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="85"/>
     </row>
     <row r="27" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B27" s="78"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="86"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="86"/>
-      <c r="J27" s="86"/>
-      <c r="K27" s="86"/>
-      <c r="L27" s="86"/>
-      <c r="M27" s="86"/>
-      <c r="N27" s="87"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="85"/>
     </row>
     <row r="28" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B28" s="78"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="86"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="86"/>
-      <c r="J28" s="86"/>
-      <c r="K28" s="86"/>
-      <c r="L28" s="86"/>
-      <c r="M28" s="86"/>
-      <c r="N28" s="87"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="78"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="85"/>
     </row>
     <row r="29" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B29" s="78"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="86"/>
-      <c r="G29" s="86"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="86"/>
-      <c r="J29" s="86"/>
-      <c r="K29" s="86"/>
-      <c r="L29" s="86"/>
-      <c r="M29" s="86"/>
-      <c r="N29" s="87"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="85"/>
     </row>
     <row r="30" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B30" s="78"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="86"/>
-      <c r="G30" s="86"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="86"/>
-      <c r="J30" s="86"/>
-      <c r="K30" s="86"/>
-      <c r="L30" s="86"/>
-      <c r="M30" s="86"/>
-      <c r="N30" s="87"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="85"/>
     </row>
     <row r="31" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B31" s="78"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="86"/>
-      <c r="G31" s="86"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="86"/>
-      <c r="J31" s="86"/>
-      <c r="K31" s="86"/>
-      <c r="L31" s="86"/>
-      <c r="M31" s="86"/>
-      <c r="N31" s="87"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="85"/>
     </row>
     <row r="32" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B32" s="78"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="86"/>
-      <c r="G32" s="86"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="86"/>
-      <c r="J32" s="86"/>
-      <c r="K32" s="86"/>
-      <c r="L32" s="86"/>
-      <c r="M32" s="86"/>
-      <c r="N32" s="87"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="84"/>
+      <c r="N32" s="85"/>
     </row>
     <row r="33" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B33" s="81"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="88"/>
-      <c r="H33" s="88"/>
-      <c r="I33" s="88"/>
-      <c r="J33" s="88"/>
-      <c r="K33" s="88"/>
-      <c r="L33" s="88"/>
-      <c r="M33" s="88"/>
-      <c r="N33" s="89"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="86"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="86"/>
+      <c r="N33" s="87"/>
     </row>
     <row r="34" spans="2:14" ht="22.05" customHeight="1"/>
   </sheetData>
@@ -19666,110 +18702,87 @@
     <mergeCell ref="B1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="D3:D5">
-    <cfRule type="containsText" dxfId="100" priority="52" operator="containsText" text="Testing">
+    <cfRule type="containsText" dxfId="90" priority="60" operator="containsText" text="Testing">
       <formula>NOT(ISERROR(SEARCH("Testing",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="99" priority="53" operator="containsText" text="On Hold">
+    <cfRule type="containsText" dxfId="89" priority="61" operator="containsText" text="On Hold">
       <formula>NOT(ISERROR(SEARCH("On Hold",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="98" priority="54" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="88" priority="62" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="97" priority="55" operator="containsText" text="Ready to Start">
+    <cfRule type="containsText" dxfId="87" priority="63" operator="containsText" text="Ready to Start">
       <formula>NOT(ISERROR(SEARCH("Ready to Start",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="96" priority="56" operator="containsText" text="In Progress">
+    <cfRule type="containsText" dxfId="86" priority="64" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6:D21">
-    <cfRule type="containsText" dxfId="95" priority="57" operator="containsText" text="Testing">
+  <conditionalFormatting sqref="D7:D21">
+    <cfRule type="containsText" dxfId="85" priority="65" operator="containsText" text="Testing">
+      <formula>NOT(ISERROR(SEARCH("Testing",D7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="84" priority="66" operator="containsText" text="On Hold">
+      <formula>NOT(ISERROR(SEARCH("On Hold",D7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="83" priority="67" operator="containsText" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",D7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="82" priority="68" operator="containsText" text="Ready to Start">
+      <formula>NOT(ISERROR(SEARCH("Ready to Start",D7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="81" priority="69" operator="containsText" text="In Progress">
+      <formula>NOT(ISERROR(SEARCH("In Progress",D7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:E21 E3:E4">
+    <cfRule type="containsText" dxfId="80" priority="70" operator="containsText" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",E3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="79" priority="71" operator="containsText" text="Medium">
+      <formula>NOT(ISERROR(SEARCH("Medium",E3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="78" priority="72" operator="containsText" text="High">
+      <formula>NOT(ISERROR(SEARCH("High",E3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5">
+    <cfRule type="containsText" dxfId="77" priority="9" operator="containsText" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="76" priority="10" operator="containsText" text="Medium">
+      <formula>NOT(ISERROR(SEARCH("Medium",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="75" priority="11" operator="containsText" text="High">
+      <formula>NOT(ISERROR(SEARCH("High",E5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="containsText" dxfId="74" priority="4" operator="containsText" text="Testing">
       <formula>NOT(ISERROR(SEARCH("Testing",D6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="94" priority="58" operator="containsText" text="On Hold">
+    <cfRule type="containsText" dxfId="73" priority="5" operator="containsText" text="On Hold">
       <formula>NOT(ISERROR(SEARCH("On Hold",D6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="93" priority="59" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="72" priority="6" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",D6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="92" priority="60" operator="containsText" text="Ready to Start">
+    <cfRule type="containsText" dxfId="71" priority="7" operator="containsText" text="Ready to Start">
       <formula>NOT(ISERROR(SEARCH("Ready to Start",D6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="91" priority="61" operator="containsText" text="In Progress">
+    <cfRule type="containsText" dxfId="70" priority="8" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E21 E3:E4">
-    <cfRule type="containsText" dxfId="90" priority="62" operator="containsText" text="Low">
-      <formula>NOT(ISERROR(SEARCH("Low",E3)))</formula>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="containsText" dxfId="69" priority="1" operator="containsText" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",E6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="89" priority="63" operator="containsText" text="Medium">
-      <formula>NOT(ISERROR(SEARCH("Medium",E3)))</formula>
+    <cfRule type="containsText" dxfId="68" priority="2" operator="containsText" text="Medium">
+      <formula>NOT(ISERROR(SEARCH("Medium",E6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="88" priority="64" operator="containsText" text="High">
-      <formula>NOT(ISERROR(SEARCH("High",E3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="containsText" dxfId="87" priority="39" operator="containsText" text="Testing">
-      <formula>NOT(ISERROR(SEARCH("Testing",E6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="86" priority="40" operator="containsText" text="On Hold">
-      <formula>NOT(ISERROR(SEARCH("On Hold",E6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="41" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",E6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="42" operator="containsText" text="Ready to Start">
-      <formula>NOT(ISERROR(SEARCH("Ready to Start",E6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="83" priority="43" operator="containsText" text="In Progress">
-      <formula>NOT(ISERROR(SEARCH("In Progress",E6)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="82" priority="34" operator="containsText" text="Testing">
-      <formula>NOT(ISERROR(SEARCH("Testing",C6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="81" priority="35" operator="containsText" text="On Hold">
-      <formula>NOT(ISERROR(SEARCH("On Hold",C6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="80" priority="36" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",C6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="79" priority="37" operator="containsText" text="Ready to Start">
-      <formula>NOT(ISERROR(SEARCH("Ready to Start",C6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="38" operator="containsText" text="In Progress">
-      <formula>NOT(ISERROR(SEARCH("In Progress",C6)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="containsText" dxfId="77" priority="29" operator="containsText" text="Testing">
-      <formula>NOT(ISERROR(SEARCH("Testing",B6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="30" operator="containsText" text="On Hold">
-      <formula>NOT(ISERROR(SEARCH("On Hold",B6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="31" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",B6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="74" priority="32" operator="containsText" text="Ready to Start">
-      <formula>NOT(ISERROR(SEARCH("Ready to Start",B6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="73" priority="33" operator="containsText" text="In Progress">
-      <formula>NOT(ISERROR(SEARCH("In Progress",B6)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="containsText" dxfId="72" priority="1" operator="containsText" text="Low">
-      <formula>NOT(ISERROR(SEARCH("Low",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="71" priority="2" operator="containsText" text="Medium">
-      <formula>NOT(ISERROR(SEARCH("Medium",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="70" priority="3" operator="containsText" text="High">
-      <formula>NOT(ISERROR(SEARCH("High",E5)))</formula>
+    <cfRule type="containsText" dxfId="67" priority="3" operator="containsText" text="High">
+      <formula>NOT(ISERROR(SEARCH("High",E6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19799,215 +18812,215 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.6">
-      <c r="B1" s="90" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
+      <c r="B1" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
     </row>
     <row r="2" spans="1:15" ht="27.6">
-      <c r="B2" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="36" t="s">
+      <c r="B2" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="G2" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="H2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="35" t="s">
         <v>8</v>
       </c>
       <c r="M2" s="11"/>
     </row>
     <row r="3" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="60" t="s">
+      <c r="A3" s="62"/>
+      <c r="B3" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="61">
-        <v>47027</v>
-      </c>
-      <c r="G3" s="61">
-        <v>47027</v>
-      </c>
-      <c r="H3" s="64">
-        <v>10</v>
-      </c>
-      <c r="I3" s="40" t="s">
-        <v>55</v>
+      <c r="F3" s="60">
+        <v>47009</v>
+      </c>
+      <c r="G3" s="60">
+        <v>47010</v>
+      </c>
+      <c r="H3" s="63">
+        <v>2</v>
+      </c>
+      <c r="I3" s="39" t="s">
+        <v>50</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="57" t="s">
+      <c r="A4" s="62"/>
+      <c r="B4" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="60">
+        <v>47010</v>
+      </c>
+      <c r="G4" s="60">
+        <v>47011</v>
+      </c>
+      <c r="H4" s="63">
+        <v>2</v>
+      </c>
+      <c r="I4" s="56" t="s">
         <v>45</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="60" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="61">
-        <v>47036</v>
-      </c>
-      <c r="G4" s="61">
-        <v>47045</v>
-      </c>
-      <c r="H4" s="64">
-        <v>10</v>
-      </c>
-      <c r="I4" s="57" t="s">
-        <v>50</v>
       </c>
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A5" s="63"/>
-      <c r="B5" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="60" t="s">
+      <c r="A5" s="62"/>
+      <c r="B5" s="95" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="61">
-        <v>47036</v>
-      </c>
-      <c r="G5" s="61">
-        <v>47042</v>
-      </c>
-      <c r="H5" s="64">
-        <v>7</v>
-      </c>
-      <c r="I5" s="57" t="s">
-        <v>53</v>
+      <c r="F5" s="60">
+        <v>47014</v>
+      </c>
+      <c r="G5" s="60">
+        <v>47014</v>
+      </c>
+      <c r="H5" s="63">
+        <v>1</v>
+      </c>
+      <c r="I5" s="56" t="s">
+        <v>48</v>
       </c>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A6" s="63"/>
-      <c r="B6" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="60" t="s">
+      <c r="A6" s="62"/>
+      <c r="B6" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="61">
-        <v>47042</v>
-      </c>
-      <c r="G6" s="61">
-        <v>47044</v>
-      </c>
-      <c r="H6" s="64">
-        <v>3</v>
-      </c>
-      <c r="I6" s="57" t="s">
-        <v>71</v>
+      <c r="F6" s="60">
+        <v>47014</v>
+      </c>
+      <c r="G6" s="60">
+        <v>47014</v>
+      </c>
+      <c r="H6" s="63">
+        <v>1</v>
+      </c>
+      <c r="I6" s="56" t="s">
+        <v>62</v>
       </c>
       <c r="M6" s="3"/>
     </row>
     <row r="7" spans="1:15" ht="21.6" customHeight="1">
-      <c r="A7" s="63"/>
-      <c r="B7" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="60" t="s">
+      <c r="A7" s="62"/>
+      <c r="B7" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="61">
-        <v>47044</v>
-      </c>
-      <c r="G7" s="61">
-        <v>47050</v>
-      </c>
-      <c r="H7" s="64">
-        <v>7</v>
-      </c>
-      <c r="I7" s="57" t="s">
-        <v>76</v>
+      <c r="F7" s="60">
+        <v>47015</v>
+      </c>
+      <c r="G7" s="60">
+        <v>47016</v>
+      </c>
+      <c r="H7" s="63">
+        <v>2</v>
+      </c>
+      <c r="I7" s="56" t="s">
+        <v>66</v>
       </c>
       <c r="M7" s="3"/>
     </row>
     <row r="8" spans="1:15" ht="21.6" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="57" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="60" t="s">
+      <c r="A8" s="62"/>
+      <c r="B8" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="61">
-        <v>47050</v>
-      </c>
-      <c r="G8" s="61">
-        <v>47052</v>
-      </c>
-      <c r="H8" s="64">
-        <v>3</v>
-      </c>
-      <c r="I8" s="57" t="s">
-        <v>77</v>
+      <c r="F8" s="60">
+        <v>47016</v>
+      </c>
+      <c r="G8" s="60">
+        <v>47017</v>
+      </c>
+      <c r="H8" s="63">
+        <v>2</v>
+      </c>
+      <c r="I8" s="56" t="s">
+        <v>67</v>
       </c>
       <c r="M8" s="3"/>
     </row>
@@ -20163,162 +19176,162 @@
       <c r="G22" s="9"/>
       <c r="H22" s="10">
         <f>MAX(G3:G21)-MIN(F3:F21)+1</f>
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="I22" s="8"/>
     </row>
     <row r="23" spans="2:14" ht="22.05" customHeight="1"/>
     <row r="24" spans="2:14" ht="45" customHeight="1">
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="76"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="84"/>
-      <c r="K24" s="84"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="84"/>
-      <c r="N24" s="85"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="82"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="83"/>
     </row>
     <row r="25" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B25" s="78"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
-      <c r="L25" s="86"/>
-      <c r="M25" s="86"/>
-      <c r="N25" s="87"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="78"/>
+      <c r="E25" s="84"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="85"/>
     </row>
     <row r="26" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B26" s="78"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
-      <c r="L26" s="86"/>
-      <c r="M26" s="86"/>
-      <c r="N26" s="87"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="85"/>
     </row>
     <row r="27" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B27" s="78"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="86"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="86"/>
-      <c r="J27" s="86"/>
-      <c r="K27" s="86"/>
-      <c r="L27" s="86"/>
-      <c r="M27" s="86"/>
-      <c r="N27" s="87"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="85"/>
     </row>
     <row r="28" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B28" s="78"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="86"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="86"/>
-      <c r="J28" s="86"/>
-      <c r="K28" s="86"/>
-      <c r="L28" s="86"/>
-      <c r="M28" s="86"/>
-      <c r="N28" s="87"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="78"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="85"/>
     </row>
     <row r="29" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B29" s="78"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="86"/>
-      <c r="G29" s="86"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="86"/>
-      <c r="J29" s="86"/>
-      <c r="K29" s="86"/>
-      <c r="L29" s="86"/>
-      <c r="M29" s="86"/>
-      <c r="N29" s="87"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="85"/>
     </row>
     <row r="30" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B30" s="78"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="86"/>
-      <c r="G30" s="86"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="86"/>
-      <c r="J30" s="86"/>
-      <c r="K30" s="86"/>
-      <c r="L30" s="86"/>
-      <c r="M30" s="86"/>
-      <c r="N30" s="87"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="85"/>
     </row>
     <row r="31" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B31" s="78"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="86"/>
-      <c r="G31" s="86"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="86"/>
-      <c r="J31" s="86"/>
-      <c r="K31" s="86"/>
-      <c r="L31" s="86"/>
-      <c r="M31" s="86"/>
-      <c r="N31" s="87"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="85"/>
     </row>
     <row r="32" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B32" s="78"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="86"/>
-      <c r="G32" s="86"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="86"/>
-      <c r="J32" s="86"/>
-      <c r="K32" s="86"/>
-      <c r="L32" s="86"/>
-      <c r="M32" s="86"/>
-      <c r="N32" s="87"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="84"/>
+      <c r="N32" s="85"/>
     </row>
     <row r="33" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B33" s="81"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="88"/>
-      <c r="H33" s="88"/>
-      <c r="I33" s="88"/>
-      <c r="J33" s="88"/>
-      <c r="K33" s="88"/>
-      <c r="L33" s="88"/>
-      <c r="M33" s="88"/>
-      <c r="N33" s="89"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="86"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="86"/>
+      <c r="N33" s="87"/>
     </row>
     <row r="34" spans="2:14" ht="22.05" customHeight="1"/>
   </sheetData>
@@ -20328,63 +19341,63 @@
     <mergeCell ref="B1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="D3:D21">
-    <cfRule type="containsText" dxfId="69" priority="52" operator="containsText" text="Testing">
+    <cfRule type="containsText" dxfId="66" priority="52" operator="containsText" text="Testing">
       <formula>NOT(ISERROR(SEARCH("Testing",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="53" operator="containsText" text="On Hold">
+    <cfRule type="containsText" dxfId="65" priority="53" operator="containsText" text="On Hold">
       <formula>NOT(ISERROR(SEARCH("On Hold",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="67" priority="54" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="64" priority="54" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="55" operator="containsText" text="Ready to Start">
+    <cfRule type="containsText" dxfId="63" priority="55" operator="containsText" text="Ready to Start">
       <formula>NOT(ISERROR(SEARCH("Ready to Start",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="65" priority="56" operator="containsText" text="In Progress">
+    <cfRule type="containsText" dxfId="62" priority="56" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E21">
-    <cfRule type="containsText" dxfId="64" priority="77" operator="containsText" text="Low">
+    <cfRule type="containsText" dxfId="61" priority="77" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",E4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="63" priority="78" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="60" priority="78" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",E4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="79" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="59" priority="79" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",E4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3">
-    <cfRule type="containsText" dxfId="61" priority="49" operator="containsText" text="Low">
+    <cfRule type="containsText" dxfId="58" priority="49" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="50" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="57" priority="50" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="51" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="56" priority="51" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E6">
-    <cfRule type="containsText" dxfId="58" priority="36" operator="containsText" text="Low">
+    <cfRule type="containsText" dxfId="55" priority="36" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="37" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="54" priority="37" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="38" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="53" priority="38" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:E8">
-    <cfRule type="containsText" dxfId="55" priority="1" operator="containsText" text="Low">
+    <cfRule type="containsText" dxfId="52" priority="1" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",E7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="2" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="51" priority="2" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",E7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="53" priority="3" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="50" priority="3" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",E7)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20415,217 +19428,158 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.6">
-      <c r="B1" s="90" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
+      <c r="B1" s="88" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
     </row>
     <row r="2" spans="1:15" ht="27.6">
-      <c r="B2" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="36" t="s">
+      <c r="B2" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="G2" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="H2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="35" t="s">
         <v>8</v>
       </c>
       <c r="M2" s="11"/>
     </row>
     <row r="3" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="60" t="s">
+      <c r="A3" s="62"/>
+      <c r="B3" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="61">
-        <v>47055</v>
-      </c>
-      <c r="G3" s="61">
-        <v>47062</v>
-      </c>
-      <c r="H3" s="64">
-        <v>8</v>
-      </c>
-      <c r="I3" s="57" t="s">
-        <v>57</v>
+      <c r="F3" s="60">
+        <v>47018</v>
+      </c>
+      <c r="G3" s="60">
+        <v>47019</v>
+      </c>
+      <c r="H3" s="63">
+        <v>2</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>52</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="57" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="62" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="61">
-        <v>47055</v>
-      </c>
-      <c r="G4" s="61">
-        <v>47062</v>
-      </c>
-      <c r="H4" s="64">
-        <v>8</v>
-      </c>
-      <c r="I4" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" s="63"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="60">
+        <v>47021</v>
+      </c>
+      <c r="G4" s="60">
+        <v>47023</v>
+      </c>
+      <c r="H4" s="63">
+        <v>3</v>
+      </c>
+      <c r="I4" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="62"/>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="1:15" s="71" customFormat="1" ht="22.05" customHeight="1">
-      <c r="A5" s="63"/>
-      <c r="B5" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="57" t="s">
+    <row r="5" spans="1:15" s="69" customFormat="1" ht="22.05" customHeight="1">
+      <c r="A5"/>
+      <c r="B5" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="62" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="61">
-        <v>47062</v>
-      </c>
-      <c r="G5" s="61">
-        <v>47070</v>
-      </c>
-      <c r="H5" s="64">
-        <v>9</v>
-      </c>
-      <c r="I5" s="57" t="s">
-        <v>85</v>
-      </c>
-      <c r="J5" s="63"/>
-      <c r="M5" s="72"/>
+      <c r="C5" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="60">
+        <v>47023</v>
+      </c>
+      <c r="G5" s="60">
+        <v>47024</v>
+      </c>
+      <c r="H5" s="63">
+        <v>2</v>
+      </c>
+      <c r="I5" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="62"/>
+      <c r="M5" s="70"/>
     </row>
     <row r="6" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A6" s="63"/>
-      <c r="B6" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="61">
-        <v>47062</v>
-      </c>
-      <c r="G6" s="61">
-        <v>47070</v>
-      </c>
-      <c r="H6" s="64">
-        <v>9</v>
-      </c>
-      <c r="I6" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" s="63"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="5"/>
+      <c r="J6" s="62"/>
       <c r="M6" s="3"/>
     </row>
     <row r="7" spans="1:15" ht="22.05" customHeight="1">
-      <c r="B7" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="60" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="61">
-        <v>47070</v>
-      </c>
-      <c r="G7" s="61">
-        <v>47075</v>
-      </c>
-      <c r="H7" s="64">
-        <v>6</v>
-      </c>
-      <c r="I7" s="57" t="s">
-        <v>51</v>
-      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="5"/>
       <c r="M7" s="3"/>
     </row>
     <row r="8" spans="1:15" ht="22.05" customHeight="1">
-      <c r="B8" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="60" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="61">
-        <v>47075</v>
-      </c>
-      <c r="G8" s="61">
-        <v>47080</v>
-      </c>
-      <c r="H8" s="64">
-        <v>6</v>
-      </c>
-      <c r="I8" s="57" t="s">
-        <v>51</v>
-      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="3"/>
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:15" ht="22.05" customHeight="1">
@@ -20780,162 +19734,162 @@
       <c r="G22" s="9"/>
       <c r="H22" s="10">
         <f>MAX(G3:G21)-MIN(F3:F21)+1</f>
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="I22" s="8"/>
     </row>
     <row r="23" spans="2:14" ht="22.05" customHeight="1"/>
     <row r="24" spans="2:14" ht="45" customHeight="1">
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="76"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="84"/>
-      <c r="K24" s="84"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="84"/>
-      <c r="N24" s="85"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="82"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="83"/>
     </row>
     <row r="25" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B25" s="78"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
-      <c r="L25" s="86"/>
-      <c r="M25" s="86"/>
-      <c r="N25" s="87"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="78"/>
+      <c r="E25" s="84"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="85"/>
     </row>
     <row r="26" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B26" s="78"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
-      <c r="L26" s="86"/>
-      <c r="M26" s="86"/>
-      <c r="N26" s="87"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="85"/>
     </row>
     <row r="27" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B27" s="78"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="86"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="86"/>
-      <c r="J27" s="86"/>
-      <c r="K27" s="86"/>
-      <c r="L27" s="86"/>
-      <c r="M27" s="86"/>
-      <c r="N27" s="87"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="85"/>
     </row>
     <row r="28" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B28" s="78"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="86"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="86"/>
-      <c r="J28" s="86"/>
-      <c r="K28" s="86"/>
-      <c r="L28" s="86"/>
-      <c r="M28" s="86"/>
-      <c r="N28" s="87"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="78"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="85"/>
     </row>
     <row r="29" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B29" s="78"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="86"/>
-      <c r="G29" s="86"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="86"/>
-      <c r="J29" s="86"/>
-      <c r="K29" s="86"/>
-      <c r="L29" s="86"/>
-      <c r="M29" s="86"/>
-      <c r="N29" s="87"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="85"/>
     </row>
     <row r="30" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B30" s="78"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="86"/>
-      <c r="G30" s="86"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="86"/>
-      <c r="J30" s="86"/>
-      <c r="K30" s="86"/>
-      <c r="L30" s="86"/>
-      <c r="M30" s="86"/>
-      <c r="N30" s="87"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="85"/>
     </row>
     <row r="31" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B31" s="78"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="86"/>
-      <c r="G31" s="86"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="86"/>
-      <c r="J31" s="86"/>
-      <c r="K31" s="86"/>
-      <c r="L31" s="86"/>
-      <c r="M31" s="86"/>
-      <c r="N31" s="87"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="85"/>
     </row>
     <row r="32" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B32" s="78"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="86"/>
-      <c r="G32" s="86"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="86"/>
-      <c r="J32" s="86"/>
-      <c r="K32" s="86"/>
-      <c r="L32" s="86"/>
-      <c r="M32" s="86"/>
-      <c r="N32" s="87"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="84"/>
+      <c r="N32" s="85"/>
     </row>
     <row r="33" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B33" s="81"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="88"/>
-      <c r="H33" s="88"/>
-      <c r="I33" s="88"/>
-      <c r="J33" s="88"/>
-      <c r="K33" s="88"/>
-      <c r="L33" s="88"/>
-      <c r="M33" s="88"/>
-      <c r="N33" s="89"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="86"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="86"/>
+      <c r="N33" s="87"/>
     </row>
     <row r="34" spans="2:14" ht="22.05" customHeight="1"/>
   </sheetData>
@@ -20944,71 +19898,60 @@
     <mergeCell ref="E24:N33"/>
     <mergeCell ref="B1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D9:D21 D4:D6">
-    <cfRule type="containsText" dxfId="52" priority="23" operator="containsText" text="Testing">
+  <conditionalFormatting sqref="D8:D21 D4">
+    <cfRule type="containsText" dxfId="49" priority="23" operator="containsText" text="Testing">
       <formula>NOT(ISERROR(SEARCH("Testing",D4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="24" operator="containsText" text="On Hold">
+    <cfRule type="containsText" dxfId="48" priority="24" operator="containsText" text="On Hold">
       <formula>NOT(ISERROR(SEARCH("On Hold",D4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="25" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="47" priority="25" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",D4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="26" operator="containsText" text="Ready to Start">
+    <cfRule type="containsText" dxfId="46" priority="26" operator="containsText" text="Ready to Start">
       <formula>NOT(ISERROR(SEARCH("Ready to Start",D4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="27" operator="containsText" text="In Progress">
+    <cfRule type="containsText" dxfId="45" priority="27" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",D4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E9:E21 E6">
-    <cfRule type="containsText" dxfId="47" priority="20" operator="containsText" text="Low">
-      <formula>NOT(ISERROR(SEARCH("Low",E6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="21" operator="containsText" text="Medium">
-      <formula>NOT(ISERROR(SEARCH("Medium",E6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="45" priority="22" operator="containsText" text="High">
-      <formula>NOT(ISERROR(SEARCH("High",E6)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E5">
-    <cfRule type="containsText" dxfId="44" priority="17" operator="containsText" text="Low">
+  <conditionalFormatting sqref="E4 E8:E21">
+    <cfRule type="containsText" dxfId="44" priority="20" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",E4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="18" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="43" priority="21" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",E4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="19" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="42" priority="22" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",E4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D8">
+  <conditionalFormatting sqref="D5">
     <cfRule type="containsText" dxfId="41" priority="9" operator="containsText" text="Testing">
-      <formula>NOT(ISERROR(SEARCH("Testing",D7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Testing",D5)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="40" priority="10" operator="containsText" text="On Hold">
-      <formula>NOT(ISERROR(SEARCH("On Hold",D7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("On Hold",D5)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="39" priority="11" operator="containsText" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",D7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Complete",D5)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="38" priority="12" operator="containsText" text="Ready to Start">
-      <formula>NOT(ISERROR(SEARCH("Ready to Start",D7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Ready to Start",D5)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="37" priority="13" operator="containsText" text="In Progress">
-      <formula>NOT(ISERROR(SEARCH("In Progress",D7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("In Progress",D5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E8">
+  <conditionalFormatting sqref="E5">
     <cfRule type="containsText" dxfId="36" priority="14" operator="containsText" text="Low">
-      <formula>NOT(ISERROR(SEARCH("Low",E7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Low",E5)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="35" priority="15" operator="containsText" text="Medium">
-      <formula>NOT(ISERROR(SEARCH("Medium",E7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Medium",E5)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="34" priority="16" operator="containsText" text="High">
-      <formula>NOT(ISERROR(SEARCH("High",E7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("High",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3">
@@ -21067,160 +20010,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.6">
-      <c r="B1" s="90" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
+      <c r="B1" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
     </row>
     <row r="2" spans="1:15" ht="27.6">
-      <c r="B2" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="36" t="s">
+      <c r="B2" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="G2" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="H2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="35" t="s">
         <v>8</v>
       </c>
       <c r="M2" s="11"/>
     </row>
     <row r="3" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="57" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="60" t="s">
+      <c r="A3" s="58"/>
+      <c r="B3" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="61">
-        <v>47083</v>
-      </c>
-      <c r="G3" s="61">
-        <v>47092</v>
-      </c>
-      <c r="H3" s="64">
-        <v>10</v>
-      </c>
-      <c r="I3" s="57" t="s">
-        <v>47</v>
+      <c r="F3" s="60">
+        <v>47025</v>
+      </c>
+      <c r="G3" s="60">
+        <v>47026</v>
+      </c>
+      <c r="H3" s="63">
+        <v>2</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>43</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="62" t="s">
+      <c r="A4" s="58"/>
+      <c r="B4" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="61">
-        <v>47092</v>
-      </c>
-      <c r="G4" s="61">
-        <v>47101</v>
-      </c>
-      <c r="H4" s="64">
-        <v>10</v>
-      </c>
-      <c r="I4" s="57" t="s">
-        <v>81</v>
+      <c r="F4" s="60">
+        <v>47028</v>
+      </c>
+      <c r="G4" s="60">
+        <v>47029</v>
+      </c>
+      <c r="H4" s="63">
+        <v>2</v>
+      </c>
+      <c r="I4" s="56" t="s">
+        <v>71</v>
       </c>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A5" s="59"/>
-      <c r="B5" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="60" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="61">
-        <v>47101</v>
-      </c>
-      <c r="G5" s="61">
-        <v>47108</v>
-      </c>
-      <c r="H5" s="64">
-        <v>8</v>
-      </c>
-      <c r="I5" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="3"/>
+    <row r="5" spans="1:15" s="69" customFormat="1" ht="22.05" customHeight="1">
+      <c r="B5" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="66" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="60">
+        <v>47029</v>
+      </c>
+      <c r="G5" s="60">
+        <v>47029</v>
+      </c>
+      <c r="H5" s="67">
+        <v>1</v>
+      </c>
+      <c r="I5" s="65" t="s">
+        <v>73</v>
+      </c>
+      <c r="M5" s="68"/>
     </row>
-    <row r="6" spans="1:15" s="71" customFormat="1" ht="22.05" customHeight="1">
-      <c r="B6" s="66" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="66" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" s="67" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="62" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="68">
-        <v>47101</v>
-      </c>
-      <c r="G6" s="68">
-        <v>47106</v>
-      </c>
-      <c r="H6" s="69">
-        <v>6</v>
-      </c>
-      <c r="I6" s="66" t="s">
-        <v>84</v>
-      </c>
-      <c r="M6" s="70"/>
+    <row r="6" spans="1:15" s="69" customFormat="1" ht="22.05" customHeight="1">
+      <c r="B6" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="66" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="60">
+        <v>47030</v>
+      </c>
+      <c r="G6" s="60">
+        <v>47032</v>
+      </c>
+      <c r="H6" s="67">
+        <v>3</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>79</v>
+      </c>
+      <c r="M6" s="68"/>
     </row>
     <row r="7" spans="1:15" ht="22.05" customHeight="1">
       <c r="B7" s="2"/>
@@ -21396,162 +20338,162 @@
       <c r="G22" s="9"/>
       <c r="H22" s="10">
         <f>MAX(G3:G21)-MIN(F3:F21)+1</f>
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="I22" s="8"/>
     </row>
     <row r="23" spans="2:14" ht="22.05" customHeight="1"/>
     <row r="24" spans="2:14" ht="45" customHeight="1">
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="76"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="84"/>
-      <c r="K24" s="84"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="84"/>
-      <c r="N24" s="85"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="82"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="83"/>
     </row>
     <row r="25" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B25" s="78"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
-      <c r="L25" s="86"/>
-      <c r="M25" s="86"/>
-      <c r="N25" s="87"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="78"/>
+      <c r="E25" s="84"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="85"/>
     </row>
     <row r="26" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B26" s="78"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
-      <c r="L26" s="86"/>
-      <c r="M26" s="86"/>
-      <c r="N26" s="87"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="85"/>
     </row>
     <row r="27" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B27" s="78"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="86"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="86"/>
-      <c r="J27" s="86"/>
-      <c r="K27" s="86"/>
-      <c r="L27" s="86"/>
-      <c r="M27" s="86"/>
-      <c r="N27" s="87"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="85"/>
     </row>
     <row r="28" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B28" s="78"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="86"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="86"/>
-      <c r="J28" s="86"/>
-      <c r="K28" s="86"/>
-      <c r="L28" s="86"/>
-      <c r="M28" s="86"/>
-      <c r="N28" s="87"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="78"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="85"/>
     </row>
     <row r="29" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B29" s="78"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="86"/>
-      <c r="G29" s="86"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="86"/>
-      <c r="J29" s="86"/>
-      <c r="K29" s="86"/>
-      <c r="L29" s="86"/>
-      <c r="M29" s="86"/>
-      <c r="N29" s="87"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="85"/>
     </row>
     <row r="30" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B30" s="78"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="86"/>
-      <c r="G30" s="86"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="86"/>
-      <c r="J30" s="86"/>
-      <c r="K30" s="86"/>
-      <c r="L30" s="86"/>
-      <c r="M30" s="86"/>
-      <c r="N30" s="87"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="85"/>
     </row>
     <row r="31" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B31" s="78"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="86"/>
-      <c r="G31" s="86"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="86"/>
-      <c r="J31" s="86"/>
-      <c r="K31" s="86"/>
-      <c r="L31" s="86"/>
-      <c r="M31" s="86"/>
-      <c r="N31" s="87"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="85"/>
     </row>
     <row r="32" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B32" s="78"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="86"/>
-      <c r="G32" s="86"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="86"/>
-      <c r="J32" s="86"/>
-      <c r="K32" s="86"/>
-      <c r="L32" s="86"/>
-      <c r="M32" s="86"/>
-      <c r="N32" s="87"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="84"/>
+      <c r="N32" s="85"/>
     </row>
     <row r="33" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B33" s="81"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="88"/>
-      <c r="H33" s="88"/>
-      <c r="I33" s="88"/>
-      <c r="J33" s="88"/>
-      <c r="K33" s="88"/>
-      <c r="L33" s="88"/>
-      <c r="M33" s="88"/>
-      <c r="N33" s="89"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="86"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="86"/>
+      <c r="N33" s="87"/>
     </row>
     <row r="34" spans="2:14" ht="22.05" customHeight="1"/>
   </sheetData>
@@ -21608,185 +20550,185 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1">
-      <c r="A1" s="19"/>
-      <c r="B1" s="91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
+      <c r="A1" s="18"/>
+      <c r="B1" s="89" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
     </row>
     <row r="2" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A2" s="20"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="20"/>
+      <c r="A3" s="19"/>
       <c r="B3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="41"/>
+      <c r="D3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
     </row>
     <row r="4" spans="1:7" ht="22.05" customHeight="1">
-      <c r="A4" s="20"/>
+      <c r="A4" s="19"/>
       <c r="B4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="41"/>
       <c r="D4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="44"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="52"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="51"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="20"/>
+      <c r="A5" s="19"/>
       <c r="B5" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="41"/>
       <c r="D5" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="52"/>
+        <v>18</v>
+      </c>
+      <c r="E5" s="43"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="51"/>
     </row>
     <row r="6" spans="1:7" ht="22.05" customHeight="1">
-      <c r="A6" s="20"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="52"/>
+        <v>19</v>
+      </c>
+      <c r="E6" s="43"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="51"/>
     </row>
     <row r="7" spans="1:7" ht="22.05" customHeight="1">
-      <c r="A7" s="20"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="42"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="41"/>
       <c r="D7" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="52"/>
+        <v>14</v>
+      </c>
+      <c r="E7" s="43"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="51"/>
     </row>
     <row r="8" spans="1:7" ht="22.05" customHeight="1">
-      <c r="A8" s="20"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="42"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="52"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="51"/>
     </row>
     <row r="9" spans="1:7" ht="22.05" customHeight="1">
-      <c r="A9" s="20"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="52"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="43"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="51"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="20"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="52"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="51"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="20"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="52"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="51"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="20"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="52"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="51"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="20"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="52"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="51"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="20"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="52"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="51"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="20"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="52"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="51"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="20"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="52"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="51"/>
     </row>
     <row r="17" spans="1:7" ht="16.2" thickBot="1">
-      <c r="A17" s="46"/>
-      <c r="B17" s="47"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="52"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="51"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="F18" s="56"/>
-      <c r="G18" s="56"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -21865,89 +20807,89 @@
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="3.296875" customWidth="1"/>
-    <col min="2" max="2" width="16.69921875" style="25" customWidth="1"/>
+    <col min="2" max="2" width="16.69921875" style="24" customWidth="1"/>
     <col min="4" max="4" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="19"/>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="31"/>
+      <c r="A1" s="18"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="30"/>
     </row>
     <row r="2" spans="1:5" ht="27.6">
-      <c r="A2" s="20"/>
-      <c r="B2" s="95" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="32"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="93" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="31"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A3" s="20"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="21"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A4" s="20"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="21"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
-      <c r="A5" s="20"/>
-      <c r="B5" s="96"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="21"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="20"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="20"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="21"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="20"/>
     </row>
     <row r="7" spans="1:5" ht="16.8">
-      <c r="A7" s="20"/>
-      <c r="B7" s="28" t="s">
+      <c r="A7" s="19"/>
+      <c r="B7" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="21"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="20"/>
     </row>
     <row r="8" spans="1:5" ht="225" customHeight="1">
-      <c r="A8" s="20"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="21"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="20"/>
     </row>
     <row r="9" spans="1:5" ht="225" customHeight="1">
-      <c r="A9" s="20"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="21"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="20"/>
     </row>
     <row r="10" spans="1:5" ht="169.05" customHeight="1">
-      <c r="A10" s="22"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="24"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="23"/>
     </row>
     <row r="11" spans="1:5" ht="225" customHeight="1"/>
     <row r="12" spans="1:5" ht="225" customHeight="1">
-      <c r="B12" s="26"/>
+      <c r="B12" s="25"/>
     </row>
     <row r="13" spans="1:5" ht="225" customHeight="1"/>
     <row r="14" spans="1:5" ht="225" customHeight="1"/>

--- a/Bes(t)Poke SE216_SoftwareProcessModel.xlsx
+++ b/Bes(t)Poke SE216_SoftwareProcessModel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\SE 216 PROJECT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E62809C4-59A6-4E4D-AA61-4A326BCA74FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE90341-7281-411F-84FA-F1A16578549B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DD0626E2-1333-F643-A88B-8507C5CC965E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{DD0626E2-1333-F643-A88B-8507C5CC965E}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBackLog" sheetId="4" r:id="rId1"/>
@@ -191,9 +191,6 @@
     <t>Both the clients and creators can post reviews and ratings after the comission process is finished.</t>
   </si>
   <si>
-    <t>Allow access to different permission sets according to the chosen role.</t>
-  </si>
-  <si>
     <t>Creator-defined order forms with multiple field types(e.g., text input, multiple choice,
 checkbox, dropdown list, and file upload (max 20MB))</t>
   </si>
@@ -362,6 +359,9 @@
   </si>
   <si>
     <t>Naz,Aslı,Zeynep</t>
+  </si>
+  <si>
+    <t>Allow access to different permission sets according to the chosen role, let the creators upload their portfolios</t>
   </si>
 </sst>
 </file>
@@ -18011,7 +18011,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="91.95" customHeight="1">
       <c r="A1" s="72" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="73"/>
     </row>
@@ -18036,7 +18036,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" customHeight="1">
@@ -18052,7 +18052,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" customHeight="1">
@@ -18068,7 +18068,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45" customHeight="1">
@@ -18076,7 +18076,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="45" customHeight="1">
@@ -18084,7 +18084,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="45" customHeight="1">
@@ -18092,7 +18092,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" customHeight="1">
@@ -18100,7 +18100,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" customHeight="1">
@@ -18124,7 +18124,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" customHeight="1">
@@ -18132,7 +18132,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="45" customHeight="1">
@@ -18156,7 +18156,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="45" customHeight="1">
@@ -18164,7 +18164,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45" customHeight="1">
@@ -18254,7 +18254,7 @@
     <row r="3" spans="1:15" ht="46.05" customHeight="1">
       <c r="A3" s="62"/>
       <c r="B3" s="56" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" s="39" t="s">
         <v>34</v>
@@ -18282,7 +18282,7 @@
     <row r="4" spans="1:15" ht="22.05" customHeight="1">
       <c r="A4" s="62"/>
       <c r="B4" s="56" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" s="39" t="s">
         <v>25</v>
@@ -18303,17 +18303,17 @@
         <v>1</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="22.05" customHeight="1">
       <c r="A5" s="62"/>
       <c r="B5" s="56" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" s="61" t="s">
         <v>18</v>
@@ -18331,14 +18331,14 @@
         <v>1</v>
       </c>
       <c r="I5" s="56" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="22.05" customHeight="1">
       <c r="A6" s="58"/>
       <c r="B6" s="56" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" s="56" t="s">
         <v>32</v>
@@ -18859,7 +18859,7 @@
     <row r="3" spans="1:15" ht="22.05" customHeight="1">
       <c r="A3" s="62"/>
       <c r="B3" s="56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="39" t="s">
         <v>41</v>
@@ -18880,14 +18880,14 @@
         <v>2</v>
       </c>
       <c r="I3" s="39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="22.05" customHeight="1">
       <c r="A4" s="62"/>
       <c r="B4" s="56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="56" t="s">
         <v>42</v>
@@ -18915,10 +18915,10 @@
     <row r="5" spans="1:15" ht="22.05" customHeight="1">
       <c r="A5" s="62"/>
       <c r="B5" s="71" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D5" s="57" t="s">
         <v>27</v>
@@ -18936,17 +18936,17 @@
         <v>1</v>
       </c>
       <c r="I5" s="56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="22.05" customHeight="1">
       <c r="A6" s="62"/>
       <c r="B6" s="56" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D6" s="57" t="s">
         <v>27</v>
@@ -18964,17 +18964,17 @@
         <v>1</v>
       </c>
       <c r="I6" s="56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M6" s="3"/>
     </row>
     <row r="7" spans="1:15" ht="21.6" customHeight="1">
       <c r="A7" s="62"/>
       <c r="B7" s="56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" s="57" t="s">
         <v>27</v>
@@ -18992,17 +18992,17 @@
         <v>2</v>
       </c>
       <c r="I7" s="56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M7" s="3"/>
     </row>
     <row r="8" spans="1:15" ht="21.6" customHeight="1">
       <c r="A8" s="62"/>
       <c r="B8" s="56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D8" s="57" t="s">
         <v>27</v>
@@ -19020,7 +19020,7 @@
         <v>2</v>
       </c>
       <c r="I8" s="56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M8" s="3"/>
     </row>
@@ -19475,10 +19475,10 @@
     <row r="3" spans="1:15" ht="22.05" customHeight="1">
       <c r="A3" s="62"/>
       <c r="B3" s="56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" s="57" t="s">
         <v>27</v>
@@ -19496,17 +19496,17 @@
         <v>2</v>
       </c>
       <c r="I3" s="56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="22.05" customHeight="1">
       <c r="A4" s="62"/>
       <c r="B4" s="56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" s="57" t="s">
         <v>27</v>
@@ -19532,10 +19532,10 @@
     <row r="5" spans="1:15" s="69" customFormat="1" ht="22.05" customHeight="1">
       <c r="A5"/>
       <c r="B5" s="56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D5" s="57" t="s">
         <v>27</v>
@@ -20057,10 +20057,10 @@
     <row r="3" spans="1:15" ht="22.05" customHeight="1">
       <c r="A3" s="58"/>
       <c r="B3" s="56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3" s="57" t="s">
         <v>27</v>
@@ -20085,10 +20085,10 @@
     <row r="4" spans="1:15" ht="22.05" customHeight="1">
       <c r="A4" s="58"/>
       <c r="B4" s="56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D4" s="57" t="s">
         <v>27</v>
@@ -20106,16 +20106,16 @@
         <v>2</v>
       </c>
       <c r="I4" s="56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:15" s="69" customFormat="1" ht="22.05" customHeight="1">
       <c r="B5" s="56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D5" s="66" t="s">
         <v>27</v>
@@ -20133,16 +20133,16 @@
         <v>1</v>
       </c>
       <c r="I5" s="65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M5" s="68"/>
     </row>
     <row r="6" spans="1:15" s="69" customFormat="1" ht="22.05" customHeight="1">
       <c r="B6" s="56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D6" s="66" t="s">
         <v>27</v>
@@ -20160,7 +20160,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="65" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M6" s="68"/>
     </row>

--- a/Bes(t)Poke SE216_SoftwareProcessModel.xlsx
+++ b/Bes(t)Poke SE216_SoftwareProcessModel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\SE 216 PROJECT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE90341-7281-411F-84FA-F1A16578549B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0296FE6-9D3C-4E99-9764-7AED843BA0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{DD0626E2-1333-F643-A88B-8507C5CC965E}"/>
+    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" activeTab="4" xr2:uid="{DD0626E2-1333-F643-A88B-8507C5CC965E}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBackLog" sheetId="4" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="87">
   <si>
     <t>BACKLOG</t>
   </si>
@@ -20034,8 +20034,8 @@
       <c r="C2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="35">
-        <v>5</v>
+      <c r="D2" s="35" t="s">
+        <v>3</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>4</v>

--- a/Bes(t)Poke SE216_SoftwareProcessModel.xlsx
+++ b/Bes(t)Poke SE216_SoftwareProcessModel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\SE 216 PROJECT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0296FE6-9D3C-4E99-9764-7AED843BA0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD0CA2A-5628-4936-95B5-409A78A01454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" activeTab="4" xr2:uid="{DD0626E2-1333-F643-A88B-8507C5CC965E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{DD0626E2-1333-F643-A88B-8507C5CC965E}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBackLog" sheetId="4" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Templates" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">ProductBackLog!$A$1:$B$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">ProductBackLog!$A$1:$B$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Sprint-1'!$B$2:$N$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Sprint-2'!$B$2:$N$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Sprint-3'!$B$2:$N$33</definedName>
@@ -122,9 +122,6 @@
     <t>#</t>
   </si>
   <si>
-    <t>Ensure the website is optimized for various devices with an engaging user interface.</t>
-  </si>
-  <si>
     <t>User Registration and Authentication</t>
   </si>
   <si>
@@ -149,9 +146,6 @@
     <t>Responsive Design &amp; UX Enhancements</t>
   </si>
   <si>
-    <t>Ensure mobile-friendly layout, improved UX.</t>
-  </si>
-  <si>
     <t>Database Planning</t>
   </si>
   <si>
@@ -174,9 +168,6 @@
   </si>
   <si>
     <t>Creator Portfolio Browsing</t>
-  </si>
-  <si>
-    <t>Creator Search &amp; Filter</t>
   </si>
   <si>
     <t>Secure payment processing(İyizico).</t>
@@ -247,9 +238,6 @@
       </rPr>
       <t>Berk Mertoğlu, Atakan Coşar, Zeynep Durmuş, Aslı ARAS, Ata Barış Kuğu, Berkay KOÇ, Eralp Çolakoğlu, Arzum Naz Güney</t>
     </r>
-  </si>
-  <si>
-    <t>Display items from the portfolio's of creators.</t>
   </si>
   <si>
     <t>Chat System</t>
@@ -355,13 +343,25 @@
     <t>All developers</t>
   </si>
   <si>
-    <t>Eralp,Berkay,Ata</t>
+    <t>Allow access to different permission sets according to the chosen role, let the creators upload their portfolios</t>
   </si>
   <si>
-    <t>Naz,Aslı,Zeynep</t>
+    <t>Display the profiles of the top creators.</t>
   </si>
   <si>
-    <t>Allow access to different permission sets according to the chosen role, let the creators upload their portfolios</t>
+    <t>Ensure the website is optimized with an engaging user interface.</t>
+  </si>
+  <si>
+    <t>Ensure user-friendly layout, improved UX.</t>
+  </si>
+  <si>
+    <t>Creator Search with tags &amp; Filter</t>
+  </si>
+  <si>
+    <t>Atakan,Aslı,Eralp</t>
+  </si>
+  <si>
+    <t>Zeynep,Berkay,Ata</t>
   </si>
 </sst>
 </file>
@@ -499,7 +499,7 @@
       <charset val="162"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Century Gothic"/>
       <family val="2"/>
@@ -1068,9 +1068,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1142,6 +1139,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -17467,222 +17467,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>220980</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>1104900</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2533030</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>32678</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="Snip Single Corner Rectangle 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5215A528-8779-47E1-82F2-A84A40DB6352}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2415540" y="8404860"/>
-          <a:ext cx="2312050" cy="1068998"/>
-        </a:xfrm>
-        <a:prstGeom prst="snip1Rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="114300" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-            <a:prstClr val="black">
-              <a:alpha val="40000"/>
-            </a:prstClr>
-          </a:outerShdw>
-        </a:effectLst>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="en-US"/>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="800" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>As a user with creator role, I want to view my commision history and the current status of the commisions I recieved, so that I can track work history and know what projects are needed to be done.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="tr-TR" sz="800" kern="1200" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>STATUS: Not Started</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="800" kern="1200" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -18003,17 +17787,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07AF4077-26B8-2245-8ED1-A0CA9934B29A}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="2" max="2" width="90.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="91.95" customHeight="1">
-      <c r="A1" s="72" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="73"/>
+      <c r="A1" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="72"/>
     </row>
     <row r="2" spans="1:2" ht="45" customHeight="1">
       <c r="A2" s="33" t="s">
@@ -18028,7 +17812,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="45" customHeight="1">
@@ -18036,7 +17820,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" customHeight="1">
@@ -18044,7 +17828,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45" customHeight="1">
@@ -18052,7 +17836,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" customHeight="1">
@@ -18060,7 +17844,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" customHeight="1">
@@ -18068,7 +17852,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45" customHeight="1">
@@ -18076,7 +17860,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="45" customHeight="1">
@@ -18084,7 +17868,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="45" customHeight="1">
@@ -18092,7 +17876,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" customHeight="1">
@@ -18100,7 +17884,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" customHeight="1">
@@ -18108,7 +17892,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="45" customHeight="1">
@@ -18116,7 +17900,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="45" customHeight="1">
@@ -18124,7 +17908,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" customHeight="1">
@@ -18132,7 +17916,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="45" customHeight="1">
@@ -18140,7 +17924,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="45" customHeight="1">
@@ -18148,7 +17932,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="45" customHeight="1">
@@ -18156,7 +17940,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="45" customHeight="1">
@@ -18164,17 +17948,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="45" customHeight="1">
-      <c r="A21" s="33">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="45" customHeight="1">
-      <c r="A22" s="33">
-        <v>20</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -18207,16 +17981,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.6">
-      <c r="B1" s="89" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
+      <c r="B1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
       <c r="J1" s="38"/>
       <c r="K1" s="38"/>
       <c r="L1" s="38"/>
@@ -18226,7 +18000,7 @@
     </row>
     <row r="2" spans="1:15" ht="27.6">
       <c r="B2" s="36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="35" t="s">
         <v>2</v>
@@ -18254,10 +18028,10 @@
     <row r="3" spans="1:15" ht="46.05" customHeight="1">
       <c r="A3" s="62"/>
       <c r="B3" s="56" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D3" s="59" t="s">
         <v>9</v>
@@ -18275,17 +18049,17 @@
         <v>3</v>
       </c>
       <c r="I3" s="56" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="22.05" customHeight="1">
       <c r="A4" s="62"/>
       <c r="B4" s="56" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="61" t="s">
         <v>18</v>
@@ -18303,17 +18077,17 @@
         <v>1</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="22.05" customHeight="1">
       <c r="A5" s="62"/>
       <c r="B5" s="56" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D5" s="61" t="s">
         <v>18</v>
@@ -18331,20 +18105,20 @@
         <v>1</v>
       </c>
       <c r="I5" s="56" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="22.05" customHeight="1">
       <c r="A6" s="58"/>
       <c r="B6" s="56" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="59" t="s">
         <v>11</v>
@@ -18359,7 +18133,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="56" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="M6" s="3"/>
     </row>
@@ -18543,156 +18317,156 @@
     </row>
     <row r="23" spans="2:14" ht="22.05" customHeight="1"/>
     <row r="24" spans="2:14" ht="45" customHeight="1">
-      <c r="B24" s="74" t="s">
+      <c r="B24" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="75"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="84"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="82"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="83"/>
     </row>
     <row r="25" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B25" s="77"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="85"/>
-      <c r="J25" s="85"/>
-      <c r="K25" s="85"/>
-      <c r="L25" s="85"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="86"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="78"/>
+      <c r="E25" s="84"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="85"/>
     </row>
     <row r="26" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B26" s="77"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="85"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="85"/>
-      <c r="L26" s="85"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="86"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="85"/>
     </row>
     <row r="27" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B27" s="77"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="85"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="85"/>
-      <c r="L27" s="85"/>
-      <c r="M27" s="85"/>
-      <c r="N27" s="86"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="85"/>
     </row>
     <row r="28" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B28" s="77"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="85"/>
-      <c r="G28" s="85"/>
-      <c r="H28" s="85"/>
-      <c r="I28" s="85"/>
-      <c r="J28" s="85"/>
-      <c r="K28" s="85"/>
-      <c r="L28" s="85"/>
-      <c r="M28" s="85"/>
-      <c r="N28" s="86"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="78"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="85"/>
     </row>
     <row r="29" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B29" s="77"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="85"/>
-      <c r="K29" s="85"/>
-      <c r="L29" s="85"/>
-      <c r="M29" s="85"/>
-      <c r="N29" s="86"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="85"/>
     </row>
     <row r="30" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B30" s="77"/>
-      <c r="C30" s="78"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="85"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="85"/>
-      <c r="I30" s="85"/>
-      <c r="J30" s="85"/>
-      <c r="K30" s="85"/>
-      <c r="L30" s="85"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="86"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="85"/>
     </row>
     <row r="31" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B31" s="77"/>
-      <c r="C31" s="78"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="85"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="85"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="85"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="85"/>
-      <c r="M31" s="85"/>
-      <c r="N31" s="86"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="85"/>
     </row>
     <row r="32" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B32" s="77"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="85"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="85"/>
-      <c r="K32" s="85"/>
-      <c r="L32" s="85"/>
-      <c r="M32" s="85"/>
-      <c r="N32" s="86"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="84"/>
+      <c r="N32" s="85"/>
     </row>
     <row r="33" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B33" s="80"/>
-      <c r="C33" s="81"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="87"/>
-      <c r="F33" s="87"/>
-      <c r="G33" s="87"/>
-      <c r="H33" s="87"/>
-      <c r="I33" s="87"/>
-      <c r="J33" s="87"/>
-      <c r="K33" s="87"/>
-      <c r="L33" s="87"/>
-      <c r="M33" s="87"/>
-      <c r="N33" s="88"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="86"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="86"/>
+      <c r="N33" s="87"/>
     </row>
     <row r="34" spans="2:14" ht="22.05" customHeight="1"/>
   </sheetData>
@@ -18812,16 +18586,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.6">
-      <c r="B1" s="89" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
+      <c r="B1" s="88" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
       <c r="J1" s="38"/>
       <c r="K1" s="38"/>
       <c r="L1" s="38"/>
@@ -18831,7 +18605,7 @@
     </row>
     <row r="2" spans="1:15" ht="27.6">
       <c r="B2" s="36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="35" t="s">
         <v>2</v>
@@ -18859,13 +18633,13 @@
     <row r="3" spans="1:15" ht="22.05" customHeight="1">
       <c r="A3" s="62"/>
       <c r="B3" s="56" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" s="57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" s="59" t="s">
         <v>10</v>
@@ -18880,20 +18654,20 @@
         <v>2</v>
       </c>
       <c r="I3" s="39" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="22.05" customHeight="1">
       <c r="A4" s="62"/>
       <c r="B4" s="56" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="59" t="s">
         <v>11</v>
@@ -18908,20 +18682,20 @@
         <v>2</v>
       </c>
       <c r="I4" s="56" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="22.05" customHeight="1">
       <c r="A5" s="62"/>
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="95" t="s">
         <v>85</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5" s="59" t="s">
         <v>11</v>
@@ -18936,20 +18710,20 @@
         <v>1</v>
       </c>
       <c r="I5" s="56" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="22.05" customHeight="1">
       <c r="A6" s="62"/>
-      <c r="B6" s="56" t="s">
-        <v>84</v>
+      <c r="B6" s="95" t="s">
+        <v>86</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="59" t="s">
         <v>11</v>
@@ -18964,20 +18738,20 @@
         <v>1</v>
       </c>
       <c r="I6" s="56" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M6" s="3"/>
     </row>
     <row r="7" spans="1:15" ht="21.6" customHeight="1">
       <c r="A7" s="62"/>
       <c r="B7" s="56" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7" s="59" t="s">
         <v>10</v>
@@ -18992,20 +18766,20 @@
         <v>2</v>
       </c>
       <c r="I7" s="56" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M7" s="3"/>
     </row>
     <row r="8" spans="1:15" ht="21.6" customHeight="1">
       <c r="A8" s="62"/>
       <c r="B8" s="56" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="59" t="s">
         <v>10</v>
@@ -19020,7 +18794,7 @@
         <v>2</v>
       </c>
       <c r="I8" s="56" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M8" s="3"/>
     </row>
@@ -19182,156 +18956,156 @@
     </row>
     <row r="23" spans="2:14" ht="22.05" customHeight="1"/>
     <row r="24" spans="2:14" ht="45" customHeight="1">
-      <c r="B24" s="74" t="s">
+      <c r="B24" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="75"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="84"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="82"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="83"/>
     </row>
     <row r="25" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B25" s="77"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="85"/>
-      <c r="J25" s="85"/>
-      <c r="K25" s="85"/>
-      <c r="L25" s="85"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="86"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="78"/>
+      <c r="E25" s="84"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="85"/>
     </row>
     <row r="26" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B26" s="77"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="85"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="85"/>
-      <c r="L26" s="85"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="86"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="85"/>
     </row>
     <row r="27" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B27" s="77"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="85"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="85"/>
-      <c r="L27" s="85"/>
-      <c r="M27" s="85"/>
-      <c r="N27" s="86"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="85"/>
     </row>
     <row r="28" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B28" s="77"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="85"/>
-      <c r="G28" s="85"/>
-      <c r="H28" s="85"/>
-      <c r="I28" s="85"/>
-      <c r="J28" s="85"/>
-      <c r="K28" s="85"/>
-      <c r="L28" s="85"/>
-      <c r="M28" s="85"/>
-      <c r="N28" s="86"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="78"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="85"/>
     </row>
     <row r="29" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B29" s="77"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="85"/>
-      <c r="K29" s="85"/>
-      <c r="L29" s="85"/>
-      <c r="M29" s="85"/>
-      <c r="N29" s="86"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="85"/>
     </row>
     <row r="30" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B30" s="77"/>
-      <c r="C30" s="78"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="85"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="85"/>
-      <c r="I30" s="85"/>
-      <c r="J30" s="85"/>
-      <c r="K30" s="85"/>
-      <c r="L30" s="85"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="86"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="85"/>
     </row>
     <row r="31" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B31" s="77"/>
-      <c r="C31" s="78"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="85"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="85"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="85"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="85"/>
-      <c r="M31" s="85"/>
-      <c r="N31" s="86"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="85"/>
     </row>
     <row r="32" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B32" s="77"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="85"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="85"/>
-      <c r="K32" s="85"/>
-      <c r="L32" s="85"/>
-      <c r="M32" s="85"/>
-      <c r="N32" s="86"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="84"/>
+      <c r="N32" s="85"/>
     </row>
     <row r="33" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B33" s="80"/>
-      <c r="C33" s="81"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="87"/>
-      <c r="F33" s="87"/>
-      <c r="G33" s="87"/>
-      <c r="H33" s="87"/>
-      <c r="I33" s="87"/>
-      <c r="J33" s="87"/>
-      <c r="K33" s="87"/>
-      <c r="L33" s="87"/>
-      <c r="M33" s="87"/>
-      <c r="N33" s="88"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="86"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="86"/>
+      <c r="N33" s="87"/>
     </row>
     <row r="34" spans="2:14" ht="22.05" customHeight="1"/>
   </sheetData>
@@ -19428,16 +19202,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.6">
-      <c r="B1" s="89" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
+      <c r="B1" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
       <c r="J1" s="38"/>
       <c r="K1" s="38"/>
       <c r="L1" s="38"/>
@@ -19447,7 +19221,7 @@
     </row>
     <row r="2" spans="1:15" ht="27.6">
       <c r="B2" s="36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="35" t="s">
         <v>2</v>
@@ -19475,13 +19249,13 @@
     <row r="3" spans="1:15" ht="22.05" customHeight="1">
       <c r="A3" s="62"/>
       <c r="B3" s="56" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3" s="57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" s="59" t="s">
         <v>11</v>
@@ -19496,20 +19270,20 @@
         <v>2</v>
       </c>
       <c r="I3" s="56" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="22.05" customHeight="1">
       <c r="A4" s="62"/>
       <c r="B4" s="56" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="59" t="s">
         <v>10</v>
@@ -19524,7 +19298,7 @@
         <v>3</v>
       </c>
       <c r="I4" s="56" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J4" s="62"/>
       <c r="M4" s="3"/>
@@ -19532,13 +19306,13 @@
     <row r="5" spans="1:15" s="69" customFormat="1" ht="22.05" customHeight="1">
       <c r="A5"/>
       <c r="B5" s="56" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5" s="59" t="s">
         <v>11</v>
@@ -19553,7 +19327,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="56" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J5" s="62"/>
       <c r="M5" s="70"/>
@@ -19740,156 +19514,156 @@
     </row>
     <row r="23" spans="2:14" ht="22.05" customHeight="1"/>
     <row r="24" spans="2:14" ht="45" customHeight="1">
-      <c r="B24" s="74" t="s">
+      <c r="B24" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="75"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="84"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="82"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="83"/>
     </row>
     <row r="25" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B25" s="77"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="85"/>
-      <c r="J25" s="85"/>
-      <c r="K25" s="85"/>
-      <c r="L25" s="85"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="86"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="78"/>
+      <c r="E25" s="84"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="85"/>
     </row>
     <row r="26" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B26" s="77"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="85"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="85"/>
-      <c r="L26" s="85"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="86"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="85"/>
     </row>
     <row r="27" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B27" s="77"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="85"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="85"/>
-      <c r="L27" s="85"/>
-      <c r="M27" s="85"/>
-      <c r="N27" s="86"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="85"/>
     </row>
     <row r="28" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B28" s="77"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="85"/>
-      <c r="G28" s="85"/>
-      <c r="H28" s="85"/>
-      <c r="I28" s="85"/>
-      <c r="J28" s="85"/>
-      <c r="K28" s="85"/>
-      <c r="L28" s="85"/>
-      <c r="M28" s="85"/>
-      <c r="N28" s="86"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="78"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="85"/>
     </row>
     <row r="29" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B29" s="77"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="85"/>
-      <c r="K29" s="85"/>
-      <c r="L29" s="85"/>
-      <c r="M29" s="85"/>
-      <c r="N29" s="86"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="85"/>
     </row>
     <row r="30" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B30" s="77"/>
-      <c r="C30" s="78"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="85"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="85"/>
-      <c r="I30" s="85"/>
-      <c r="J30" s="85"/>
-      <c r="K30" s="85"/>
-      <c r="L30" s="85"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="86"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="85"/>
     </row>
     <row r="31" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B31" s="77"/>
-      <c r="C31" s="78"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="85"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="85"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="85"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="85"/>
-      <c r="M31" s="85"/>
-      <c r="N31" s="86"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="85"/>
     </row>
     <row r="32" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B32" s="77"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="85"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="85"/>
-      <c r="K32" s="85"/>
-      <c r="L32" s="85"/>
-      <c r="M32" s="85"/>
-      <c r="N32" s="86"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="84"/>
+      <c r="N32" s="85"/>
     </row>
     <row r="33" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B33" s="80"/>
-      <c r="C33" s="81"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="87"/>
-      <c r="F33" s="87"/>
-      <c r="G33" s="87"/>
-      <c r="H33" s="87"/>
-      <c r="I33" s="87"/>
-      <c r="J33" s="87"/>
-      <c r="K33" s="87"/>
-      <c r="L33" s="87"/>
-      <c r="M33" s="87"/>
-      <c r="N33" s="88"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="86"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="86"/>
+      <c r="N33" s="87"/>
     </row>
     <row r="34" spans="2:14" ht="22.05" customHeight="1"/>
   </sheetData>
@@ -20010,16 +19784,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.6">
-      <c r="B1" s="89" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
+      <c r="B1" s="88" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
       <c r="J1" s="38"/>
       <c r="K1" s="38"/>
       <c r="L1" s="38"/>
@@ -20029,7 +19803,7 @@
     </row>
     <row r="2" spans="1:15" ht="27.6">
       <c r="B2" s="36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="35" t="s">
         <v>2</v>
@@ -20057,13 +19831,13 @@
     <row r="3" spans="1:15" ht="22.05" customHeight="1">
       <c r="A3" s="58"/>
       <c r="B3" s="56" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D3" s="57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" s="59" t="s">
         <v>10</v>
@@ -20078,20 +19852,20 @@
         <v>2</v>
       </c>
       <c r="I3" s="56" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="22.05" customHeight="1">
       <c r="A4" s="58"/>
       <c r="B4" s="56" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="61" t="s">
         <v>13</v>
@@ -20106,19 +19880,19 @@
         <v>2</v>
       </c>
       <c r="I4" s="56" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:15" s="69" customFormat="1" ht="22.05" customHeight="1">
       <c r="B5" s="56" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D5" s="66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5" s="61" t="s">
         <v>13</v>
@@ -20133,19 +19907,19 @@
         <v>1</v>
       </c>
       <c r="I5" s="65" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="M5" s="68"/>
     </row>
     <row r="6" spans="1:15" s="69" customFormat="1" ht="22.05" customHeight="1">
       <c r="B6" s="56" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="59" t="s">
         <v>10</v>
@@ -20160,7 +19934,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="65" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="M6" s="68"/>
     </row>
@@ -20344,156 +20118,156 @@
     </row>
     <row r="23" spans="2:14" ht="22.05" customHeight="1"/>
     <row r="24" spans="2:14" ht="45" customHeight="1">
-      <c r="B24" s="74" t="s">
+      <c r="B24" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="75"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="84"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="82"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="83"/>
     </row>
     <row r="25" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B25" s="77"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="85"/>
-      <c r="J25" s="85"/>
-      <c r="K25" s="85"/>
-      <c r="L25" s="85"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="86"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="78"/>
+      <c r="E25" s="84"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="85"/>
     </row>
     <row r="26" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B26" s="77"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="85"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="85"/>
-      <c r="L26" s="85"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="86"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="85"/>
     </row>
     <row r="27" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B27" s="77"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="85"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="85"/>
-      <c r="L27" s="85"/>
-      <c r="M27" s="85"/>
-      <c r="N27" s="86"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="85"/>
     </row>
     <row r="28" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B28" s="77"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="85"/>
-      <c r="G28" s="85"/>
-      <c r="H28" s="85"/>
-      <c r="I28" s="85"/>
-      <c r="J28" s="85"/>
-      <c r="K28" s="85"/>
-      <c r="L28" s="85"/>
-      <c r="M28" s="85"/>
-      <c r="N28" s="86"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="78"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="85"/>
     </row>
     <row r="29" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B29" s="77"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="85"/>
-      <c r="K29" s="85"/>
-      <c r="L29" s="85"/>
-      <c r="M29" s="85"/>
-      <c r="N29" s="86"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="85"/>
     </row>
     <row r="30" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B30" s="77"/>
-      <c r="C30" s="78"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="85"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="85"/>
-      <c r="I30" s="85"/>
-      <c r="J30" s="85"/>
-      <c r="K30" s="85"/>
-      <c r="L30" s="85"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="86"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="85"/>
     </row>
     <row r="31" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B31" s="77"/>
-      <c r="C31" s="78"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="85"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="85"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="85"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="85"/>
-      <c r="M31" s="85"/>
-      <c r="N31" s="86"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="85"/>
     </row>
     <row r="32" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B32" s="77"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="85"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="85"/>
-      <c r="K32" s="85"/>
-      <c r="L32" s="85"/>
-      <c r="M32" s="85"/>
-      <c r="N32" s="86"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="84"/>
+      <c r="N32" s="85"/>
     </row>
     <row r="33" spans="2:14" ht="22.05" customHeight="1">
-      <c r="B33" s="80"/>
-      <c r="C33" s="81"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="87"/>
-      <c r="F33" s="87"/>
-      <c r="G33" s="87"/>
-      <c r="H33" s="87"/>
-      <c r="I33" s="87"/>
-      <c r="J33" s="87"/>
-      <c r="K33" s="87"/>
-      <c r="L33" s="87"/>
-      <c r="M33" s="87"/>
-      <c r="N33" s="88"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="86"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="86"/>
+      <c r="N33" s="87"/>
     </row>
     <row r="34" spans="2:14" ht="22.05" customHeight="1"/>
   </sheetData>
@@ -20551,21 +20325,21 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1">
       <c r="A1" s="18"/>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="91"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="90"/>
       <c r="F1" s="49"/>
       <c r="G1" s="49"/>
     </row>
     <row r="2" spans="1:7" ht="27.75" customHeight="1">
       <c r="A2" s="19"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="93"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="92"/>
       <c r="F2" s="49"/>
       <c r="G2" s="49"/>
     </row>
@@ -20648,7 +20422,7 @@
       <c r="B9" s="41"/>
       <c r="C9" s="41"/>
       <c r="D9" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="43"/>
       <c r="F9" s="54"/>
@@ -20820,32 +20594,32 @@
     </row>
     <row r="2" spans="1:5" ht="27.6">
       <c r="A2" s="19"/>
-      <c r="B2" s="94" t="s">
+      <c r="B2" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
       <c r="E2" s="31"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
       <c r="A3" s="19"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
       <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="19"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
       <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
       <c r="A5" s="19"/>
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
       <c r="E5" s="20"/>
     </row>
     <row r="6" spans="1:5">
